--- a/research/traditional_assets/database/data/turkey/turkey_advertising.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_advertising.xlsx
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1531,22 +1531,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1716691953778638</v>
+        <v>0.1712737723894191</v>
       </c>
       <c r="C2">
-        <v>61.72726732390885</v>
+        <v>61.27699499959951</v>
       </c>
       <c r="D2">
-        <v>52.99726732390885</v>
+        <v>53.16428499959951</v>
       </c>
       <c r="E2">
-        <v>-0.529</v>
+        <v>0.08829000000000009</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6172900000000001</v>
       </c>
       <c r="G2">
         <v>8.73</v>
@@ -1567,28 +1567,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.031049687</v>
       </c>
       <c r="N2">
-        <v>8.449999999999999</v>
+        <v>8.418950313</v>
       </c>
       <c r="O2">
-        <v>2.1125</v>
+        <v>2.10473757825</v>
       </c>
       <c r="P2">
-        <v>6.337499999999999</v>
+        <v>6.31421273475</v>
       </c>
       <c r="Q2">
-        <v>6.267500000000001</v>
+        <v>6.244212734750001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1716691953778638</v>
+        <v>0.1726227498883021</v>
       </c>
       <c r="T2">
-        <v>1.217251318914063</v>
+        <v>1.226472919814927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>272.1444502806099</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1712737723894191</v>
+        <v>0.1708783494009744</v>
       </c>
       <c r="C3">
-        <v>61.27699499959951</v>
+        <v>60.82777869543694</v>
       </c>
       <c r="D3">
-        <v>53.16428499959951</v>
+        <v>53.33235869543694</v>
       </c>
       <c r="E3">
-        <v>0.08829000000000009</v>
+        <v>0.7055800000000002</v>
       </c>
       <c r="F3">
-        <v>0.6172900000000001</v>
+        <v>1.23458</v>
       </c>
       <c r="G3">
         <v>8.73</v>
@@ -1649,28 +1649,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M3">
-        <v>0.031049687</v>
+        <v>0.06209937400000001</v>
       </c>
       <c r="N3">
-        <v>8.418950313</v>
+        <v>8.387900625999999</v>
       </c>
       <c r="O3">
-        <v>2.10473757825</v>
+        <v>2.0969751565</v>
       </c>
       <c r="P3">
-        <v>6.31421273475</v>
+        <v>6.290925469499999</v>
       </c>
       <c r="Q3">
-        <v>6.244212734750001</v>
+        <v>6.220925469500001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1726227498883021</v>
+        <v>0.1735957646948719</v>
       </c>
       <c r="T3">
-        <v>1.226472919814927</v>
+        <v>1.235882716652543</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>272.1444502806099</v>
+        <v>136.0722251403049</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1695,22 +1695,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1708783494009744</v>
+        <v>0.1704829264125298</v>
       </c>
       <c r="C4">
-        <v>60.82777869543694</v>
+        <v>60.37962845869833</v>
       </c>
       <c r="D4">
-        <v>53.33235869543694</v>
+        <v>53.50149845869833</v>
       </c>
       <c r="E4">
-        <v>0.7055800000000002</v>
+        <v>1.32287</v>
       </c>
       <c r="F4">
-        <v>1.23458</v>
+        <v>1.85187</v>
       </c>
       <c r="G4">
         <v>8.73</v>
@@ -1731,28 +1731,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M4">
-        <v>0.06209937400000001</v>
+        <v>0.09314906100000001</v>
       </c>
       <c r="N4">
-        <v>8.387900625999999</v>
+        <v>8.356850938999999</v>
       </c>
       <c r="O4">
-        <v>2.0969751565</v>
+        <v>2.08921273475</v>
       </c>
       <c r="P4">
-        <v>6.290925469499999</v>
+        <v>6.26763820425</v>
       </c>
       <c r="Q4">
-        <v>6.220925469500001</v>
+        <v>6.197638204250001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1735957646948719</v>
+        <v>0.1745888416624019</v>
       </c>
       <c r="T4">
-        <v>1.235882716652543</v>
+        <v>1.245486529919801</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>136.0722251403049</v>
+        <v>90.71481676020329</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1777,22 +1777,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1704829264125298</v>
+        <v>0.1700875034240852</v>
       </c>
       <c r="C5">
-        <v>60.37962845869833</v>
+        <v>59.93255446452328</v>
       </c>
       <c r="D5">
-        <v>53.50149845869833</v>
+        <v>53.67171446452328</v>
       </c>
       <c r="E5">
-        <v>1.32287</v>
+        <v>1.940160000000001</v>
       </c>
       <c r="F5">
-        <v>1.85187</v>
+        <v>2.46916</v>
       </c>
       <c r="G5">
         <v>8.73</v>
@@ -1813,28 +1813,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M5">
-        <v>0.09314906100000001</v>
+        <v>0.124198748</v>
       </c>
       <c r="N5">
-        <v>8.356850938999999</v>
+        <v>8.325801252</v>
       </c>
       <c r="O5">
-        <v>2.08921273475</v>
+        <v>2.081450313</v>
       </c>
       <c r="P5">
-        <v>6.26763820425</v>
+        <v>6.244350939</v>
       </c>
       <c r="Q5">
-        <v>6.197638204250001</v>
+        <v>6.174350939000002</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1745888416624019</v>
+        <v>0.175602607733422</v>
       </c>
       <c r="T5">
-        <v>1.245486529919801</v>
+        <v>1.255290422630127</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>90.71481676020329</v>
+        <v>68.03611257015247</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1859,22 +1859,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1700875034240852</v>
+        <v>0.1696920804356405</v>
       </c>
       <c r="C6">
-        <v>59.93255446452328</v>
+        <v>59.48656701795434</v>
       </c>
       <c r="D6">
-        <v>53.67171446452328</v>
+        <v>53.84301701795435</v>
       </c>
       <c r="E6">
-        <v>1.940160000000001</v>
+        <v>2.557450000000001</v>
       </c>
       <c r="F6">
-        <v>2.46916</v>
+        <v>3.086450000000001</v>
       </c>
       <c r="G6">
         <v>8.73</v>
@@ -1895,28 +1895,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M6">
-        <v>0.124198748</v>
+        <v>0.155248435</v>
       </c>
       <c r="N6">
-        <v>8.325801252</v>
+        <v>8.294751564999999</v>
       </c>
       <c r="O6">
-        <v>2.081450313</v>
+        <v>2.07368789125</v>
       </c>
       <c r="P6">
-        <v>6.244350939</v>
+        <v>6.221063673749999</v>
       </c>
       <c r="Q6">
-        <v>6.174350939000002</v>
+        <v>6.15106367375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.175602607733422</v>
+        <v>0.1766377162480426</v>
       </c>
       <c r="T6">
-        <v>1.255290422630127</v>
+        <v>1.265300713081723</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>68.03611257015247</v>
+        <v>54.42889005612196</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1696920804356405</v>
+        <v>0.1692966574471958</v>
       </c>
       <c r="C7">
-        <v>59.48656701795434</v>
+        <v>59.04167655601649</v>
       </c>
       <c r="D7">
-        <v>53.84301701795435</v>
+        <v>54.01541655601649</v>
       </c>
       <c r="E7">
-        <v>2.557450000000001</v>
+        <v>3.174740000000001</v>
       </c>
       <c r="F7">
-        <v>3.086450000000001</v>
+        <v>3.703740000000001</v>
       </c>
       <c r="G7">
         <v>8.73</v>
@@ -1977,28 +1977,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M7">
-        <v>0.155248435</v>
+        <v>0.186298122</v>
       </c>
       <c r="N7">
-        <v>8.294751564999999</v>
+        <v>8.263701877999999</v>
       </c>
       <c r="O7">
-        <v>2.07368789125</v>
+        <v>2.0659254695</v>
       </c>
       <c r="P7">
-        <v>6.221063673749999</v>
+        <v>6.197776408499999</v>
       </c>
       <c r="Q7">
-        <v>6.15106367375</v>
+        <v>6.127776408500001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1766377162480426</v>
+        <v>0.1776948483480807</v>
       </c>
       <c r="T7">
-        <v>1.265300713081723</v>
+        <v>1.275523988436545</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.42889005612196</v>
+        <v>45.35740838010164</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2023,22 +2023,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1692966574471958</v>
+        <v>0.1689012344587512</v>
       </c>
       <c r="C8">
-        <v>59.04167655601649</v>
+        <v>58.59789364983705</v>
       </c>
       <c r="D8">
-        <v>54.01541655601649</v>
+        <v>54.18892364983706</v>
       </c>
       <c r="E8">
-        <v>3.17474</v>
+        <v>3.79203</v>
       </c>
       <c r="F8">
-        <v>3.70374</v>
+        <v>4.32103</v>
       </c>
       <c r="G8">
         <v>8.73</v>
@@ -2059,28 +2059,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M8">
-        <v>0.186298122</v>
+        <v>0.217347809</v>
       </c>
       <c r="N8">
-        <v>8.263701877999999</v>
+        <v>8.232652191</v>
       </c>
       <c r="O8">
-        <v>2.0659254695</v>
+        <v>2.05816304775</v>
       </c>
       <c r="P8">
-        <v>6.197776408499999</v>
+        <v>6.17448914325</v>
       </c>
       <c r="Q8">
-        <v>6.127776408500001</v>
+        <v>6.104489143250001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1776948483480807</v>
+        <v>0.1787747144717755</v>
       </c>
       <c r="T8">
-        <v>1.275523988436545</v>
+        <v>1.285967119175341</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.35740838010165</v>
+        <v>38.8777786115157</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1689012344587512</v>
+        <v>0.1685058114703065</v>
       </c>
       <c r="C9">
-        <v>58.59789364983707</v>
+        <v>58.15522900680641</v>
       </c>
       <c r="D9">
-        <v>54.18892364983706</v>
+        <v>54.36354900680642</v>
       </c>
       <c r="E9">
-        <v>3.792030000000001</v>
+        <v>4.409320000000001</v>
       </c>
       <c r="F9">
-        <v>4.321030000000001</v>
+        <v>4.938320000000001</v>
       </c>
       <c r="G9">
         <v>8.73</v>
@@ -2141,28 +2141,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M9">
-        <v>0.2173478090000001</v>
+        <v>0.248397496</v>
       </c>
       <c r="N9">
-        <v>8.232652191</v>
+        <v>8.201602503999998</v>
       </c>
       <c r="O9">
-        <v>2.05816304775</v>
+        <v>2.050400626</v>
       </c>
       <c r="P9">
-        <v>6.17448914325</v>
+        <v>6.151201877999998</v>
       </c>
       <c r="Q9">
-        <v>6.104489143250001</v>
+        <v>6.081201878</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1787747144717755</v>
+        <v>0.1798780559459854</v>
       </c>
       <c r="T9">
-        <v>1.285967119175341</v>
+        <v>1.296637274495415</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.87777861151569</v>
+        <v>34.01805628507623</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1685058114703065</v>
+        <v>0.1681103884818618</v>
       </c>
       <c r="C10">
-        <v>58.15522900680641</v>
+        <v>57.71369347278066</v>
       </c>
       <c r="D10">
-        <v>54.36354900680642</v>
+        <v>54.53930347278066</v>
       </c>
       <c r="E10">
-        <v>4.409320000000001</v>
+        <v>5.026610000000001</v>
       </c>
       <c r="F10">
-        <v>4.938320000000001</v>
+        <v>5.555610000000001</v>
       </c>
       <c r="G10">
         <v>8.73</v>
@@ -2223,28 +2223,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M10">
-        <v>0.248397496</v>
+        <v>0.279447183</v>
       </c>
       <c r="N10">
-        <v>8.201602503999998</v>
+        <v>8.170552816999999</v>
       </c>
       <c r="O10">
-        <v>2.050400626</v>
+        <v>2.04263820425</v>
       </c>
       <c r="P10">
-        <v>6.151201877999998</v>
+        <v>6.127914612749999</v>
       </c>
       <c r="Q10">
-        <v>6.081201878</v>
+        <v>6.05791461275</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1798780559459854</v>
+        <v>0.1810056466833647</v>
       </c>
       <c r="T10">
-        <v>1.296637274495415</v>
+        <v>1.307541938723622</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.01805628507623</v>
+        <v>30.23827225340109</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2269,22 +2269,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1681103884818618</v>
+        <v>0.1677149654934172</v>
       </c>
       <c r="C11">
-        <v>57.71369347278066</v>
+        <v>57.273298034327</v>
       </c>
       <c r="D11">
-        <v>54.53930347278066</v>
+        <v>54.716198034327</v>
       </c>
       <c r="E11">
-        <v>5.026610000000001</v>
+        <v>5.6439</v>
       </c>
       <c r="F11">
-        <v>5.555610000000001</v>
+        <v>6.1729</v>
       </c>
       <c r="G11">
         <v>8.73</v>
@@ -2305,28 +2305,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M11">
-        <v>0.279447183</v>
+        <v>0.31049687</v>
       </c>
       <c r="N11">
-        <v>8.170552816999999</v>
+        <v>8.13950313</v>
       </c>
       <c r="O11">
-        <v>2.04263820425</v>
+        <v>2.0348757825</v>
       </c>
       <c r="P11">
-        <v>6.127914612749999</v>
+        <v>6.104627347499999</v>
       </c>
       <c r="Q11">
-        <v>6.05791461275</v>
+        <v>6.034627347500001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1810056466833647</v>
+        <v>0.1821582949926857</v>
       </c>
       <c r="T11">
-        <v>1.307541938723622</v>
+        <v>1.318688928823568</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.23827225340109</v>
+        <v>27.21444502806099</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2351,22 +2351,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1677149654934172</v>
+        <v>0.1673195425049725</v>
       </c>
       <c r="C12">
-        <v>57.273298034327</v>
+        <v>56.83405382101335</v>
       </c>
       <c r="D12">
-        <v>54.716198034327</v>
+        <v>54.89424382101335</v>
       </c>
       <c r="E12">
-        <v>5.643900000000001</v>
+        <v>6.261190000000001</v>
       </c>
       <c r="F12">
-        <v>6.172900000000001</v>
+        <v>6.790190000000001</v>
       </c>
       <c r="G12">
         <v>8.73</v>
@@ -2387,28 +2387,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M12">
-        <v>0.31049687</v>
+        <v>0.341546557</v>
       </c>
       <c r="N12">
-        <v>8.13950313</v>
+        <v>8.108453442999998</v>
       </c>
       <c r="O12">
-        <v>2.0348757825</v>
+        <v>2.02711336075</v>
       </c>
       <c r="P12">
-        <v>6.104627347499999</v>
+        <v>6.081340082249999</v>
       </c>
       <c r="Q12">
-        <v>6.034627347500001</v>
+        <v>6.01134008225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1821582949926857</v>
+        <v>0.1833368455112051</v>
       </c>
       <c r="T12">
-        <v>1.318688928823568</v>
+        <v>1.330086413083063</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.21444502806099</v>
+        <v>24.74040457096453</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1673195425049725</v>
+        <v>0.1669241195165279</v>
       </c>
       <c r="C13">
-        <v>56.83405382101335</v>
+        <v>56.39597210774236</v>
       </c>
       <c r="D13">
-        <v>54.89424382101335</v>
+        <v>55.07345210774236</v>
       </c>
       <c r="E13">
-        <v>6.261190000000001</v>
+        <v>6.878480000000001</v>
       </c>
       <c r="F13">
-        <v>6.790190000000001</v>
+        <v>7.407480000000001</v>
       </c>
       <c r="G13">
         <v>8.73</v>
@@ -2469,28 +2469,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M13">
-        <v>0.341546557</v>
+        <v>0.372596244</v>
       </c>
       <c r="N13">
-        <v>8.108453442999998</v>
+        <v>8.077403755999999</v>
       </c>
       <c r="O13">
-        <v>2.02711336075</v>
+        <v>2.019350939</v>
       </c>
       <c r="P13">
-        <v>6.081340082249999</v>
+        <v>6.058052816999999</v>
       </c>
       <c r="Q13">
-        <v>6.01134008225</v>
+        <v>5.988052817000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1833368455112051</v>
+        <v>0.1845421812687817</v>
       </c>
       <c r="T13">
-        <v>1.330086413083063</v>
+        <v>1.341742931075728</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.74040457096453</v>
+        <v>22.67870419005082</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1669241195165279</v>
+        <v>0.1665286965280832</v>
       </c>
       <c r="C14">
-        <v>56.39597210774236</v>
+        <v>55.95906431713151</v>
       </c>
       <c r="D14">
-        <v>55.07345210774236</v>
+        <v>55.25383431713151</v>
       </c>
       <c r="E14">
-        <v>6.878480000000001</v>
+        <v>7.495770000000002</v>
       </c>
       <c r="F14">
-        <v>7.407480000000001</v>
+        <v>8.024770000000002</v>
       </c>
       <c r="G14">
         <v>8.73</v>
@@ -2551,28 +2551,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M14">
-        <v>0.372596244</v>
+        <v>0.4036459310000001</v>
       </c>
       <c r="N14">
-        <v>8.077403755999999</v>
+        <v>8.046354068999999</v>
       </c>
       <c r="O14">
-        <v>2.019350939</v>
+        <v>2.01158851725</v>
       </c>
       <c r="P14">
-        <v>6.058052816999999</v>
+        <v>6.03476555175</v>
       </c>
       <c r="Q14">
-        <v>5.988052817000001</v>
+        <v>5.964765551750001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1845421812687817</v>
+        <v>0.1857752258943485</v>
       </c>
       <c r="T14">
-        <v>1.341742931075728</v>
+        <v>1.353667414999259</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.67870419005082</v>
+        <v>20.93418848312383</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2597,22 +2597,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1665286965280832</v>
+        <v>0.1661332735396385</v>
       </c>
       <c r="C15">
-        <v>55.95906431713151</v>
+        <v>55.52334202194018</v>
       </c>
       <c r="D15">
-        <v>55.25383431713151</v>
+        <v>55.43540202194018</v>
       </c>
       <c r="E15">
-        <v>7.495770000000002</v>
+        <v>8.113060000000003</v>
       </c>
       <c r="F15">
-        <v>8.024770000000002</v>
+        <v>8.642060000000003</v>
       </c>
       <c r="G15">
         <v>8.73</v>
@@ -2633,28 +2633,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M15">
-        <v>0.4036459310000001</v>
+        <v>0.4346956180000001</v>
       </c>
       <c r="N15">
-        <v>8.046354068999999</v>
+        <v>8.015304382</v>
       </c>
       <c r="O15">
-        <v>2.01158851725</v>
+        <v>2.0038260955</v>
       </c>
       <c r="P15">
-        <v>6.03476555175</v>
+        <v>6.0114782865</v>
       </c>
       <c r="Q15">
-        <v>5.964765551750001</v>
+        <v>5.941478286500002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1857752258943485</v>
+        <v>0.1870369459763239</v>
       </c>
       <c r="T15">
-        <v>1.353667414999259</v>
+        <v>1.365869212502408</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.93418848312383</v>
+        <v>19.43888930575785</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1661332735396385</v>
+        <v>0.1657378505511939</v>
       </c>
       <c r="C16">
-        <v>55.52334202194018</v>
+        <v>55.08881694754464</v>
       </c>
       <c r="D16">
-        <v>55.43540202194018</v>
+        <v>55.61816694754464</v>
       </c>
       <c r="E16">
-        <v>8.113060000000003</v>
+        <v>8.730350000000003</v>
       </c>
       <c r="F16">
-        <v>8.642060000000003</v>
+        <v>9.259350000000003</v>
       </c>
       <c r="G16">
         <v>8.73</v>
@@ -2715,28 +2715,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M16">
-        <v>0.4346956180000001</v>
+        <v>0.4657453050000001</v>
       </c>
       <c r="N16">
-        <v>8.015304382</v>
+        <v>7.984254694999999</v>
       </c>
       <c r="O16">
-        <v>2.0038260955</v>
+        <v>1.99606367375</v>
       </c>
       <c r="P16">
-        <v>6.0114782865</v>
+        <v>5.98819102125</v>
       </c>
       <c r="Q16">
-        <v>5.941478286500002</v>
+        <v>5.918191021250001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1870369459763239</v>
+        <v>0.1883283535896399</v>
       </c>
       <c r="T16">
-        <v>1.365869212502408</v>
+        <v>1.378358111123277</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.43888930575785</v>
+        <v>18.14296335204066</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1657378505511939</v>
+        <v>0.1653424275627492</v>
       </c>
       <c r="C17">
-        <v>55.08881694754464</v>
+        <v>54.65550097446214</v>
       </c>
       <c r="D17">
-        <v>55.61816694754464</v>
+        <v>55.80214097446213</v>
       </c>
       <c r="E17">
-        <v>8.730350000000001</v>
+        <v>9.347640000000002</v>
       </c>
       <c r="F17">
-        <v>9.259350000000001</v>
+        <v>9.876640000000002</v>
       </c>
       <c r="G17">
         <v>8.73</v>
@@ -2797,28 +2797,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M17">
-        <v>0.4657453050000001</v>
+        <v>0.496794992</v>
       </c>
       <c r="N17">
-        <v>7.984254694999999</v>
+        <v>7.953205007999999</v>
       </c>
       <c r="O17">
-        <v>1.99606367375</v>
+        <v>1.988301252</v>
       </c>
       <c r="P17">
-        <v>5.98819102125</v>
+        <v>5.964903756</v>
       </c>
       <c r="Q17">
-        <v>5.918191021250001</v>
+        <v>5.894903756000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1883283535896399</v>
+        <v>0.1896505090032729</v>
       </c>
       <c r="T17">
-        <v>1.378358111123277</v>
+        <v>1.391144364473215</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.14296335204066</v>
+        <v>17.00902814253812</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2843,22 +2843,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1653424275627492</v>
+        <v>0.1649470045743046</v>
       </c>
       <c r="C18">
-        <v>54.65550097446214</v>
+        <v>54.22340614092533</v>
       </c>
       <c r="D18">
-        <v>55.80214097446213</v>
+        <v>55.98733614092534</v>
       </c>
       <c r="E18">
-        <v>9.347640000000002</v>
+        <v>9.964930000000003</v>
       </c>
       <c r="F18">
-        <v>9.876640000000002</v>
+        <v>10.49393</v>
       </c>
       <c r="G18">
         <v>8.73</v>
@@ -2879,28 +2879,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M18">
-        <v>0.496794992</v>
+        <v>0.5278446790000001</v>
       </c>
       <c r="N18">
-        <v>7.953205007999999</v>
+        <v>7.922155320999999</v>
       </c>
       <c r="O18">
-        <v>1.988301252</v>
+        <v>1.98053883025</v>
       </c>
       <c r="P18">
-        <v>5.964903756</v>
+        <v>5.94161649075</v>
       </c>
       <c r="Q18">
-        <v>5.894903756000001</v>
+        <v>5.871616490750001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1896505090032729</v>
+        <v>0.1910045235834995</v>
       </c>
       <c r="T18">
-        <v>1.391144364473215</v>
+        <v>1.404238720313512</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.00902814253812</v>
+        <v>16.00849707532999</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2925,22 +2925,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1649470045743046</v>
+        <v>0.1645515815858599</v>
       </c>
       <c r="C19">
-        <v>54.22340614092533</v>
+        <v>53.79254464550819</v>
       </c>
       <c r="D19">
-        <v>55.98733614092534</v>
+        <v>56.17376464550819</v>
       </c>
       <c r="E19">
-        <v>9.964930000000003</v>
+        <v>10.58222</v>
       </c>
       <c r="F19">
-        <v>10.49393</v>
+        <v>11.11122</v>
       </c>
       <c r="G19">
         <v>8.73</v>
@@ -2961,28 +2961,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M19">
-        <v>0.5278446790000001</v>
+        <v>0.5588943660000001</v>
       </c>
       <c r="N19">
-        <v>7.922155320999999</v>
+        <v>7.891105633999999</v>
       </c>
       <c r="O19">
-        <v>1.98053883025</v>
+        <v>1.9727764085</v>
       </c>
       <c r="P19">
-        <v>5.94161649075</v>
+        <v>5.918329225499999</v>
       </c>
       <c r="Q19">
-        <v>5.871616490750001</v>
+        <v>5.848329225500001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1910045235834995</v>
+        <v>0.1923915629095852</v>
       </c>
       <c r="T19">
-        <v>1.404238720313512</v>
+        <v>1.4176524506865</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.00849707532999</v>
+        <v>15.11913612670055</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3007,22 +3007,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1645515815858599</v>
+        <v>0.1641561585974153</v>
       </c>
       <c r="C20">
-        <v>53.79254464550819</v>
+        <v>53.36292884980428</v>
       </c>
       <c r="D20">
-        <v>56.17376464550819</v>
+        <v>56.36143884980427</v>
       </c>
       <c r="E20">
-        <v>10.58222</v>
+        <v>11.19951</v>
       </c>
       <c r="F20">
-        <v>11.11122</v>
+        <v>11.72851</v>
       </c>
       <c r="G20">
         <v>8.73</v>
@@ -3043,28 +3043,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M20">
-        <v>0.5588943660000001</v>
+        <v>0.5899440530000001</v>
       </c>
       <c r="N20">
-        <v>7.891105633999999</v>
+        <v>7.860055946999999</v>
       </c>
       <c r="O20">
-        <v>1.9727764085</v>
+        <v>1.96501398675</v>
       </c>
       <c r="P20">
-        <v>5.918329225499999</v>
+        <v>5.895041960249999</v>
       </c>
       <c r="Q20">
-        <v>5.848329225500001</v>
+        <v>5.825041960250001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1923915629095852</v>
+        <v>0.1938128501202658</v>
       </c>
       <c r="T20">
-        <v>1.4176524506865</v>
+        <v>1.431397384278574</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.11913612670055</v>
+        <v>14.3233921200321</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3089,22 +3089,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1641561585974153</v>
+        <v>0.1637607356089706</v>
       </c>
       <c r="C21">
-        <v>53.36292884980428</v>
+        <v>52.93457128115933</v>
       </c>
       <c r="D21">
-        <v>56.36143884980427</v>
+        <v>56.55037128115933</v>
       </c>
       <c r="E21">
-        <v>11.19951</v>
+        <v>11.8168</v>
       </c>
       <c r="F21">
-        <v>11.72851</v>
+        <v>12.3458</v>
       </c>
       <c r="G21">
         <v>8.73</v>
@@ -3125,28 +3125,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M21">
-        <v>0.5899440530000001</v>
+        <v>0.6209937400000001</v>
       </c>
       <c r="N21">
-        <v>7.860055946999999</v>
+        <v>7.829006259999999</v>
       </c>
       <c r="O21">
-        <v>1.96501398675</v>
+        <v>1.957251565</v>
       </c>
       <c r="P21">
-        <v>5.895041960249999</v>
+        <v>5.871754694999999</v>
       </c>
       <c r="Q21">
-        <v>5.825041960250001</v>
+        <v>5.801754695000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1938128501202658</v>
+        <v>0.1952696695112132</v>
       </c>
       <c r="T21">
-        <v>1.431397384278574</v>
+        <v>1.445485941210449</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.3233921200321</v>
+        <v>13.60722251403049</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3171,22 +3171,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1637607356089706</v>
+        <v>0.1633653126205259</v>
       </c>
       <c r="C22">
-        <v>52.93457128115933</v>
+        <v>52.50748463545846</v>
       </c>
       <c r="D22">
-        <v>56.55037128115933</v>
+        <v>56.74057463545847</v>
       </c>
       <c r="E22">
-        <v>11.8168</v>
+        <v>12.43409</v>
       </c>
       <c r="F22">
-        <v>12.3458</v>
+        <v>12.96309</v>
       </c>
       <c r="G22">
         <v>8.73</v>
@@ -3207,28 +3207,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M22">
-        <v>0.6209937400000001</v>
+        <v>0.6520434270000001</v>
       </c>
       <c r="N22">
-        <v>7.829006259999999</v>
+        <v>7.797956573</v>
       </c>
       <c r="O22">
-        <v>1.957251565</v>
+        <v>1.94948914325</v>
       </c>
       <c r="P22">
-        <v>5.871754694999999</v>
+        <v>5.848467429749999</v>
       </c>
       <c r="Q22">
-        <v>5.801754695000001</v>
+        <v>5.778467429750001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1952696695112132</v>
+        <v>0.196763370405729</v>
       </c>
       <c r="T22">
-        <v>1.445485941210449</v>
+        <v>1.459931170469714</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.60722251403049</v>
+        <v>12.9592595371719</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3253,22 +3253,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1633653126205259</v>
+        <v>0.1632173896320813</v>
       </c>
       <c r="C23">
-        <v>52.50748463545846</v>
+        <v>51.96167668247418</v>
       </c>
       <c r="D23">
-        <v>56.74057463545847</v>
+        <v>56.81205668247419</v>
       </c>
       <c r="E23">
-        <v>12.43409</v>
+        <v>13.05138</v>
       </c>
       <c r="F23">
-        <v>12.96309</v>
+        <v>13.58038</v>
       </c>
       <c r="G23">
         <v>8.73</v>
@@ -3289,45 +3289,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M23">
-        <v>0.6520434270000001</v>
+        <v>0.703463684</v>
       </c>
       <c r="N23">
-        <v>7.797956573</v>
+        <v>7.746536315999999</v>
       </c>
       <c r="O23">
-        <v>1.94948914325</v>
+        <v>1.936634079</v>
       </c>
       <c r="P23">
-        <v>5.848467429749999</v>
+        <v>5.809902236999999</v>
       </c>
       <c r="Q23">
-        <v>5.778467429750001</v>
+        <v>5.739902237000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.196763370405729</v>
+        <v>0.1982953713231811</v>
       </c>
       <c r="T23">
-        <v>1.459931170469714</v>
+        <v>1.474746790222807</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.9592595371719</v>
+        <v>12.01199179458992</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3335,22 +3335,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1632173896320813</v>
+        <v>0.1628332166436366</v>
       </c>
       <c r="C24">
-        <v>51.96167668247418</v>
+        <v>51.53087781910467</v>
       </c>
       <c r="D24">
-        <v>56.81205668247419</v>
+        <v>56.99854781910468</v>
       </c>
       <c r="E24">
-        <v>13.05138</v>
+        <v>13.66867</v>
       </c>
       <c r="F24">
-        <v>13.58038</v>
+        <v>14.19767</v>
       </c>
       <c r="G24">
         <v>8.73</v>
@@ -3371,28 +3371,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M24">
-        <v>0.703463684</v>
+        <v>0.7354393060000001</v>
       </c>
       <c r="N24">
-        <v>7.746536315999999</v>
+        <v>7.714560693999999</v>
       </c>
       <c r="O24">
-        <v>1.936634079</v>
+        <v>1.9286401735</v>
       </c>
       <c r="P24">
-        <v>5.809902236999999</v>
+        <v>5.785920520499999</v>
       </c>
       <c r="Q24">
-        <v>5.739902237000001</v>
+        <v>5.715920520500001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1982953713231811</v>
+        <v>0.1998671644722553</v>
       </c>
       <c r="T24">
-        <v>1.474746790222807</v>
+        <v>1.489947231268187</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.01199179458992</v>
+        <v>11.48973128178167</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3417,22 +3417,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1628332166436366</v>
+        <v>0.1624490436551919</v>
       </c>
       <c r="C25">
-        <v>51.53087781910467</v>
+        <v>51.10130733884114</v>
       </c>
       <c r="D25">
-        <v>56.99854781910468</v>
+        <v>57.18626733884114</v>
       </c>
       <c r="E25">
-        <v>13.66867</v>
+        <v>14.28596</v>
       </c>
       <c r="F25">
-        <v>14.19767</v>
+        <v>14.81496</v>
       </c>
       <c r="G25">
         <v>8.73</v>
@@ -3453,28 +3453,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M25">
-        <v>0.7354393060000001</v>
+        <v>0.7674149280000001</v>
       </c>
       <c r="N25">
-        <v>7.714560693999999</v>
+        <v>7.682585071999999</v>
       </c>
       <c r="O25">
-        <v>1.9286401735</v>
+        <v>1.920646268</v>
       </c>
       <c r="P25">
-        <v>5.785920520499999</v>
+        <v>5.761938804</v>
       </c>
       <c r="Q25">
-        <v>5.715920520500001</v>
+        <v>5.691938804000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1998671644722553</v>
+        <v>0.2014803205989368</v>
       </c>
       <c r="T25">
-        <v>1.489947231268187</v>
+        <v>1.505547683920025</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.48973128178167</v>
+        <v>11.0109924783741</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3499,22 +3499,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1624490436551919</v>
+        <v>0.1620648706667473</v>
       </c>
       <c r="C26">
-        <v>51.10130733884114</v>
+        <v>50.67297741849004</v>
       </c>
       <c r="D26">
-        <v>57.18626733884114</v>
+        <v>57.37522741849004</v>
       </c>
       <c r="E26">
-        <v>14.28596</v>
+        <v>14.90325</v>
       </c>
       <c r="F26">
-        <v>14.81496</v>
+        <v>15.43225</v>
       </c>
       <c r="G26">
         <v>8.73</v>
@@ -3535,28 +3535,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M26">
-        <v>0.767414928</v>
+        <v>0.79939055</v>
       </c>
       <c r="N26">
-        <v>7.682585071999999</v>
+        <v>7.650609449999999</v>
       </c>
       <c r="O26">
-        <v>1.920646268</v>
+        <v>1.9126523625</v>
       </c>
       <c r="P26">
-        <v>5.761938804</v>
+        <v>5.7379570875</v>
       </c>
       <c r="Q26">
-        <v>5.691938804000001</v>
+        <v>5.667957087500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2014803205989368</v>
+        <v>0.2031364942223297</v>
       </c>
       <c r="T26">
-        <v>1.505547683920025</v>
+        <v>1.521564148642578</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.0109924783741</v>
+        <v>10.57055277923913</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3581,22 +3581,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1620648706667473</v>
+        <v>0.1616806976783026</v>
       </c>
       <c r="C27">
-        <v>50.67297741849004</v>
+        <v>50.24590039633424</v>
       </c>
       <c r="D27">
-        <v>57.37522741849004</v>
+        <v>57.56544039633424</v>
       </c>
       <c r="E27">
-        <v>14.90325</v>
+        <v>15.52054</v>
       </c>
       <c r="F27">
-        <v>15.43225</v>
+        <v>16.04954</v>
       </c>
       <c r="G27">
         <v>8.73</v>
@@ -3617,28 +3617,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M27">
-        <v>0.79939055</v>
+        <v>0.8313661720000002</v>
       </c>
       <c r="N27">
-        <v>7.650609449999999</v>
+        <v>7.618633827999999</v>
       </c>
       <c r="O27">
-        <v>1.9126523625</v>
+        <v>1.904658457</v>
       </c>
       <c r="P27">
-        <v>5.7379570875</v>
+        <v>5.713975370999999</v>
       </c>
       <c r="Q27">
-        <v>5.667957087500001</v>
+        <v>5.643975371000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2031364942223297</v>
+        <v>0.2048374292950036</v>
       </c>
       <c r="T27">
-        <v>1.521564148642578</v>
+        <v>1.538013490790066</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.57055277923913</v>
+        <v>10.1639930569607</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1616806976783026</v>
+        <v>0.161640774689858</v>
       </c>
       <c r="C28">
-        <v>50.24590039633424</v>
+        <v>49.64844956279275</v>
       </c>
       <c r="D28">
-        <v>57.56544039633424</v>
+        <v>57.58527956279276</v>
       </c>
       <c r="E28">
-        <v>15.52054</v>
+        <v>16.13783</v>
       </c>
       <c r="F28">
-        <v>16.04954</v>
+        <v>16.66683</v>
       </c>
       <c r="G28">
         <v>8.73</v>
@@ -3699,45 +3699,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M28">
-        <v>0.8313661720000002</v>
+        <v>0.8916754050000002</v>
       </c>
       <c r="N28">
-        <v>7.618633827999999</v>
+        <v>7.558324594999999</v>
       </c>
       <c r="O28">
-        <v>1.904658457</v>
+        <v>1.88958114875</v>
       </c>
       <c r="P28">
-        <v>5.713975370999999</v>
+        <v>5.66874344625</v>
       </c>
       <c r="Q28">
-        <v>5.643975371000001</v>
+        <v>5.598743446250001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2048374292950036</v>
+        <v>0.2065849653285726</v>
       </c>
       <c r="T28">
-        <v>1.538013490790066</v>
+        <v>1.554913499845704</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>10.1639930569607</v>
+        <v>9.476542643900778</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.161640774689858</v>
+        <v>0.1612693517014133</v>
       </c>
       <c r="C29">
-        <v>49.64844956279275</v>
+        <v>49.21639050338848</v>
       </c>
       <c r="D29">
-        <v>57.58527956279276</v>
+        <v>57.77051050338849</v>
       </c>
       <c r="E29">
-        <v>16.13783</v>
+        <v>16.75512000000001</v>
       </c>
       <c r="F29">
-        <v>16.66683</v>
+        <v>17.28412000000001</v>
       </c>
       <c r="G29">
         <v>8.73</v>
@@ -3781,28 +3781,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M29">
-        <v>0.8916754050000002</v>
+        <v>0.9247004200000003</v>
       </c>
       <c r="N29">
-        <v>7.558324594999999</v>
+        <v>7.525299579999999</v>
       </c>
       <c r="O29">
-        <v>1.88958114875</v>
+        <v>1.881324895</v>
       </c>
       <c r="P29">
-        <v>5.66874344625</v>
+        <v>5.643974684999999</v>
       </c>
       <c r="Q29">
-        <v>5.598743446250001</v>
+        <v>5.573974685</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2065849653285726</v>
+        <v>0.2083810440297407</v>
       </c>
       <c r="T29">
-        <v>1.554913499845704</v>
+        <v>1.572282953597331</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.476542643900778</v>
+        <v>9.138094692332892</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3827,22 +3827,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1612693517014133</v>
+        <v>0.1608979287129687</v>
       </c>
       <c r="C30">
-        <v>49.21639050338848</v>
+        <v>48.78552693082361</v>
       </c>
       <c r="D30">
-        <v>57.77051050338849</v>
+        <v>57.95693693082362</v>
       </c>
       <c r="E30">
-        <v>16.75512000000001</v>
+        <v>17.37241000000001</v>
       </c>
       <c r="F30">
-        <v>17.28412000000001</v>
+        <v>17.90141000000001</v>
       </c>
       <c r="G30">
         <v>8.73</v>
@@ -3863,28 +3863,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M30">
-        <v>0.9247004200000003</v>
+        <v>0.9577254350000003</v>
       </c>
       <c r="N30">
-        <v>7.525299579999999</v>
+        <v>7.492274564999999</v>
       </c>
       <c r="O30">
-        <v>1.881324895</v>
+        <v>1.87306864125</v>
       </c>
       <c r="P30">
-        <v>5.643974684999999</v>
+        <v>5.619205923749999</v>
       </c>
       <c r="Q30">
-        <v>5.573974685</v>
+        <v>5.549205923750001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2083810440297407</v>
+        <v>0.2102277164971389</v>
       </c>
       <c r="T30">
-        <v>1.572282953597331</v>
+        <v>1.590141687736328</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.138094692332892</v>
+        <v>8.822987978804171</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3909,22 +3909,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1608979287129686</v>
+        <v>0.160526505724524</v>
       </c>
       <c r="C31">
-        <v>48.78552693082364</v>
+        <v>48.35587045613672</v>
       </c>
       <c r="D31">
-        <v>57.95693693082364</v>
+        <v>58.14457045613673</v>
       </c>
       <c r="E31">
-        <v>17.37241</v>
+        <v>17.9897</v>
       </c>
       <c r="F31">
-        <v>17.90141</v>
+        <v>18.5187</v>
       </c>
       <c r="G31">
         <v>8.73</v>
@@ -3945,28 +3945,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M31">
-        <v>0.9577254350000001</v>
+        <v>0.9907504500000002</v>
       </c>
       <c r="N31">
-        <v>7.492274564999999</v>
+        <v>7.459249549999999</v>
       </c>
       <c r="O31">
-        <v>1.87306864125</v>
+        <v>1.8648123875</v>
       </c>
       <c r="P31">
-        <v>5.619205923749999</v>
+        <v>5.594437162499999</v>
       </c>
       <c r="Q31">
-        <v>5.549205923750001</v>
+        <v>5.524437162500001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2102277164971389</v>
+        <v>0.2121271510350343</v>
       </c>
       <c r="T31">
-        <v>1.590141687736328</v>
+        <v>1.608510671422154</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.822987978804175</v>
+        <v>8.5288883795107</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3991,22 +3991,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.160526505724524</v>
+        <v>0.1601550827360793</v>
       </c>
       <c r="C32">
-        <v>48.35587045613672</v>
+        <v>47.92743284121603</v>
       </c>
       <c r="D32">
-        <v>58.14457045613673</v>
+        <v>58.33342284121603</v>
       </c>
       <c r="E32">
-        <v>17.9897</v>
+        <v>18.60699</v>
       </c>
       <c r="F32">
-        <v>18.5187</v>
+        <v>19.13599</v>
       </c>
       <c r="G32">
         <v>8.73</v>
@@ -4027,28 +4027,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M32">
-        <v>0.9907504500000002</v>
+        <v>1.023775465</v>
       </c>
       <c r="N32">
-        <v>7.459249549999999</v>
+        <v>7.426224534999999</v>
       </c>
       <c r="O32">
-        <v>1.8648123875</v>
+        <v>1.85655613375</v>
       </c>
       <c r="P32">
-        <v>5.594437162499999</v>
+        <v>5.56966840125</v>
       </c>
       <c r="Q32">
-        <v>5.524437162500001</v>
+        <v>5.499668401250001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2121271510350343</v>
+        <v>0.2140816416464918</v>
       </c>
       <c r="T32">
-        <v>1.608510671422154</v>
+        <v>1.627412089417714</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.5288883795107</v>
+        <v>8.253762947913582</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4073,22 +4073,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1601550827360793</v>
+        <v>0.1597836597476346</v>
       </c>
       <c r="C33">
-        <v>47.92743284121603</v>
+        <v>47.50022600125722</v>
       </c>
       <c r="D33">
-        <v>58.33342284121603</v>
+        <v>58.52350600125722</v>
       </c>
       <c r="E33">
-        <v>18.60699</v>
+        <v>19.22428</v>
       </c>
       <c r="F33">
-        <v>19.13599</v>
+        <v>19.75328</v>
       </c>
       <c r="G33">
         <v>8.73</v>
@@ -4109,28 +4109,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M33">
-        <v>1.023775465</v>
+        <v>1.05680048</v>
       </c>
       <c r="N33">
-        <v>7.426224534999999</v>
+        <v>7.39319952</v>
       </c>
       <c r="O33">
-        <v>1.85655613375</v>
+        <v>1.84829988</v>
       </c>
       <c r="P33">
-        <v>5.56966840125</v>
+        <v>5.54489964</v>
       </c>
       <c r="Q33">
-        <v>5.499668401250001</v>
+        <v>5.474899640000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2140816416464918</v>
+        <v>0.2160936172759333</v>
       </c>
       <c r="T33">
-        <v>1.627412089417714</v>
+        <v>1.646869431471967</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.253762947913582</v>
+        <v>7.995832855791283</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4155,22 +4155,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1597836597476346</v>
+        <v>0.15941223675919</v>
       </c>
       <c r="C34">
-        <v>47.50022600125722</v>
+        <v>47.0742620072694</v>
       </c>
       <c r="D34">
-        <v>58.52350600125722</v>
+        <v>58.7148320072694</v>
       </c>
       <c r="E34">
-        <v>19.22428</v>
+        <v>19.84157</v>
       </c>
       <c r="F34">
-        <v>19.75328</v>
+        <v>20.37057</v>
       </c>
       <c r="G34">
         <v>8.73</v>
@@ -4191,28 +4191,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M34">
-        <v>1.05680048</v>
+        <v>1.089825495</v>
       </c>
       <c r="N34">
-        <v>7.39319952</v>
+        <v>7.360174504999999</v>
       </c>
       <c r="O34">
-        <v>1.84829988</v>
+        <v>1.84004362625</v>
       </c>
       <c r="P34">
-        <v>5.54489964</v>
+        <v>5.520130878749999</v>
       </c>
       <c r="Q34">
-        <v>5.474899640000001</v>
+        <v>5.45013087875</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2160936172759333</v>
+        <v>0.2181656518793881</v>
       </c>
       <c r="T34">
-        <v>1.646869431471967</v>
+        <v>1.666907589706944</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.995832855791283</v>
+        <v>7.753534890464274</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4237,22 +4237,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.15941223675919</v>
+        <v>0.1592448137707453</v>
       </c>
       <c r="C35">
-        <v>47.0742620072694</v>
+        <v>46.54362394237283</v>
       </c>
       <c r="D35">
-        <v>58.7148320072694</v>
+        <v>58.80148394237283</v>
       </c>
       <c r="E35">
-        <v>19.84157</v>
+        <v>20.45886</v>
       </c>
       <c r="F35">
-        <v>20.37057</v>
+        <v>20.98786</v>
       </c>
       <c r="G35">
         <v>8.73</v>
@@ -4273,45 +4273,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M35">
-        <v>1.089825495</v>
+        <v>1.139640798</v>
       </c>
       <c r="N35">
-        <v>7.360174504999999</v>
+        <v>7.310359201999999</v>
       </c>
       <c r="O35">
-        <v>1.84004362625</v>
+        <v>1.8275898005</v>
       </c>
       <c r="P35">
-        <v>5.520130878749999</v>
+        <v>5.482769401499999</v>
       </c>
       <c r="Q35">
-        <v>5.45013087875</v>
+        <v>5.4127694015</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2181656518793881</v>
+        <v>0.2203004754102202</v>
       </c>
       <c r="T35">
-        <v>1.666907589706944</v>
+        <v>1.687552964858133</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.753534890464274</v>
+        <v>7.414616969512878</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4319,22 +4319,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1592448137707453</v>
+        <v>0.1588793907823007</v>
       </c>
       <c r="C36">
-        <v>46.54362394237283</v>
+        <v>46.11635454505337</v>
       </c>
       <c r="D36">
-        <v>58.80148394237283</v>
+        <v>58.99150454505337</v>
       </c>
       <c r="E36">
-        <v>20.45886</v>
+        <v>21.07615000000001</v>
       </c>
       <c r="F36">
-        <v>20.98786</v>
+        <v>21.60515000000001</v>
       </c>
       <c r="G36">
         <v>8.73</v>
@@ -4355,28 +4355,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M36">
-        <v>1.139640798</v>
+        <v>1.173159645</v>
       </c>
       <c r="N36">
-        <v>7.310359201999999</v>
+        <v>7.276840354999999</v>
       </c>
       <c r="O36">
-        <v>1.8275898005</v>
+        <v>1.81921008875</v>
       </c>
       <c r="P36">
-        <v>5.482769401499999</v>
+        <v>5.45763026625</v>
       </c>
       <c r="Q36">
-        <v>5.4127694015</v>
+        <v>5.387630266250001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2203004754102202</v>
+        <v>0.2225009858189242</v>
       </c>
       <c r="T36">
-        <v>1.687552964858133</v>
+        <v>1.708833582321665</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.414616969512878</v>
+        <v>7.202770770383938</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4401,22 +4401,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1588793907823007</v>
+        <v>0.158513967793856</v>
       </c>
       <c r="C37">
-        <v>46.11635454505337</v>
+        <v>45.69031725583653</v>
       </c>
       <c r="D37">
-        <v>58.99150454505337</v>
+        <v>59.18275725583654</v>
       </c>
       <c r="E37">
-        <v>21.07615000000001</v>
+        <v>21.69344000000001</v>
       </c>
       <c r="F37">
-        <v>21.60515000000001</v>
+        <v>22.22244000000001</v>
       </c>
       <c r="G37">
         <v>8.73</v>
@@ -4437,28 +4437,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M37">
-        <v>1.173159645</v>
+        <v>1.206678492</v>
       </c>
       <c r="N37">
-        <v>7.276840354999999</v>
+        <v>7.243321507999999</v>
       </c>
       <c r="O37">
-        <v>1.81921008875</v>
+        <v>1.810830377</v>
       </c>
       <c r="P37">
-        <v>5.45763026625</v>
+        <v>5.432491130999999</v>
       </c>
       <c r="Q37">
-        <v>5.387630266250001</v>
+        <v>5.362491131000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2225009858189242</v>
+        <v>0.2247702621779001</v>
       </c>
       <c r="T37">
-        <v>1.708833582321665</v>
+        <v>1.730779219080933</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.202770770383938</v>
+        <v>7.002693804539939</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4483,22 +4483,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.158513967793856</v>
+        <v>0.1581485448054114</v>
       </c>
       <c r="C38">
-        <v>45.69031725583652</v>
+        <v>45.2655240973246</v>
       </c>
       <c r="D38">
-        <v>59.18275725583653</v>
+        <v>59.3752540973246</v>
       </c>
       <c r="E38">
-        <v>21.69344</v>
+        <v>22.31073</v>
       </c>
       <c r="F38">
-        <v>22.22244</v>
+        <v>22.83973</v>
       </c>
       <c r="G38">
         <v>8.73</v>
@@ -4519,28 +4519,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M38">
-        <v>1.206678492</v>
+        <v>1.240197339</v>
       </c>
       <c r="N38">
-        <v>7.243321507999999</v>
+        <v>7.209802660999999</v>
       </c>
       <c r="O38">
-        <v>1.810830377</v>
+        <v>1.80245066525</v>
       </c>
       <c r="P38">
-        <v>5.432491130999999</v>
+        <v>5.40735199575</v>
       </c>
       <c r="Q38">
-        <v>5.362491131000001</v>
+        <v>5.337351995750002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2247702621779001</v>
+        <v>0.2271115790562085</v>
       </c>
       <c r="T38">
-        <v>1.730779219080933</v>
+        <v>1.753421542721448</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.00269380453994</v>
+        <v>6.813431809822644</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4565,22 +4565,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1581485448054114</v>
+        <v>0.1577831218169667</v>
       </c>
       <c r="C39">
-        <v>45.2655240973246</v>
+        <v>44.84198724904839</v>
       </c>
       <c r="D39">
-        <v>59.3752540973246</v>
+        <v>59.56900724904838</v>
       </c>
       <c r="E39">
-        <v>22.31073</v>
+        <v>22.92802</v>
       </c>
       <c r="F39">
-        <v>22.83973</v>
+        <v>23.45702</v>
       </c>
       <c r="G39">
         <v>8.73</v>
@@ -4601,28 +4601,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M39">
-        <v>1.240197339</v>
+        <v>1.273716186</v>
       </c>
       <c r="N39">
-        <v>7.209802660999999</v>
+        <v>7.176283814</v>
       </c>
       <c r="O39">
-        <v>1.80245066525</v>
+        <v>1.7940709535</v>
       </c>
       <c r="P39">
-        <v>5.40735199575</v>
+        <v>5.382212860499999</v>
       </c>
       <c r="Q39">
-        <v>5.337351995750002</v>
+        <v>5.312212860500001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2271115790562085</v>
+        <v>0.2295284222854302</v>
       </c>
       <c r="T39">
-        <v>1.753421542721448</v>
+        <v>1.776794263898753</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.813431809822644</v>
+        <v>6.634130972722049</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4647,22 +4647,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1577831218169667</v>
+        <v>0.1574176988285221</v>
       </c>
       <c r="C40">
-        <v>44.84198724904839</v>
+        <v>44.41971905003597</v>
       </c>
       <c r="D40">
-        <v>59.56900724904838</v>
+        <v>59.76402905003598</v>
       </c>
       <c r="E40">
-        <v>22.92802</v>
+        <v>23.54531</v>
       </c>
       <c r="F40">
-        <v>23.45702</v>
+        <v>24.07431</v>
       </c>
       <c r="G40">
         <v>8.73</v>
@@ -4683,28 +4683,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M40">
-        <v>1.273716186</v>
+        <v>1.307235033</v>
       </c>
       <c r="N40">
-        <v>7.176283814</v>
+        <v>7.142764966999999</v>
       </c>
       <c r="O40">
-        <v>1.7940709535</v>
+        <v>1.78569124175</v>
       </c>
       <c r="P40">
-        <v>5.382212860499999</v>
+        <v>5.357073725249999</v>
       </c>
       <c r="Q40">
-        <v>5.312212860500001</v>
+        <v>5.287073725250001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2295284222854302</v>
+        <v>0.2320245062762657</v>
       </c>
       <c r="T40">
-        <v>1.776794263898753</v>
+        <v>1.800933303803183</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.634130972722049</v>
+        <v>6.46402505034456</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4729,22 +4729,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1574176988285221</v>
+        <v>0.1570522758400774</v>
       </c>
       <c r="C41">
-        <v>44.41971905003597</v>
+        <v>43.99873200143222</v>
       </c>
       <c r="D41">
-        <v>59.76402905003598</v>
+        <v>59.96033200143223</v>
       </c>
       <c r="E41">
-        <v>23.54531</v>
+        <v>24.1626</v>
       </c>
       <c r="F41">
-        <v>24.07431</v>
+        <v>24.6916</v>
       </c>
       <c r="G41">
         <v>8.73</v>
@@ -4765,28 +4765,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M41">
-        <v>1.307235033</v>
+        <v>1.34075388</v>
       </c>
       <c r="N41">
-        <v>7.142764966999999</v>
+        <v>7.109246119999999</v>
       </c>
       <c r="O41">
-        <v>1.78569124175</v>
+        <v>1.77731153</v>
       </c>
       <c r="P41">
-        <v>5.357073725249999</v>
+        <v>5.331934589999999</v>
       </c>
       <c r="Q41">
-        <v>5.287073725250001</v>
+        <v>5.261934590000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2320245062762657</v>
+        <v>0.2346037930667957</v>
       </c>
       <c r="T41">
-        <v>1.800933303803183</v>
+        <v>1.825876978371094</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.46402505034456</v>
+        <v>6.302424424085946</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1570522758400774</v>
+        <v>0.1566868528516328</v>
       </c>
       <c r="C42">
-        <v>43.99873200143222</v>
+        <v>43.57903876917</v>
       </c>
       <c r="D42">
-        <v>59.96033200143223</v>
+        <v>60.15792876917</v>
       </c>
       <c r="E42">
-        <v>24.1626</v>
+        <v>24.77989000000001</v>
       </c>
       <c r="F42">
-        <v>24.6916</v>
+        <v>25.30889000000001</v>
       </c>
       <c r="G42">
         <v>8.73</v>
@@ -4847,28 +4847,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M42">
-        <v>1.34075388</v>
+        <v>1.374272727</v>
       </c>
       <c r="N42">
-        <v>7.109246119999999</v>
+        <v>7.075727272999999</v>
       </c>
       <c r="O42">
-        <v>1.77731153</v>
+        <v>1.76893181825</v>
       </c>
       <c r="P42">
-        <v>5.331934589999999</v>
+        <v>5.30679545475</v>
       </c>
       <c r="Q42">
-        <v>5.261934590000001</v>
+        <v>5.236795454750001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2346037930667957</v>
+        <v>0.2372705133078521</v>
       </c>
       <c r="T42">
-        <v>1.825876978371094</v>
+        <v>1.851666201229443</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.302424424085946</v>
+        <v>6.148706755205801</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4893,22 +4893,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1566868528516328</v>
+        <v>0.1566364298631881</v>
       </c>
       <c r="C43">
-        <v>43.57903876917</v>
+        <v>42.98911650873838</v>
       </c>
       <c r="D43">
-        <v>60.15792876917</v>
+        <v>60.18529650873838</v>
       </c>
       <c r="E43">
-        <v>24.77989000000001</v>
+        <v>25.39718000000001</v>
       </c>
       <c r="F43">
-        <v>25.30889000000001</v>
+        <v>25.92618000000001</v>
       </c>
       <c r="G43">
         <v>8.73</v>
@@ -4929,45 +4929,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M43">
-        <v>1.374272727</v>
+        <v>1.433717754</v>
       </c>
       <c r="N43">
-        <v>7.075727272999999</v>
+        <v>7.016282245999999</v>
       </c>
       <c r="O43">
-        <v>1.76893181825</v>
+        <v>1.7540705615</v>
       </c>
       <c r="P43">
-        <v>5.30679545475</v>
+        <v>5.2622116845</v>
       </c>
       <c r="Q43">
-        <v>5.236795454750001</v>
+        <v>5.192211684500001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2372705133078521</v>
+        <v>0.2400291894192898</v>
       </c>
       <c r="T43">
-        <v>1.851666201229443</v>
+        <v>1.878344707634631</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.148706755205801</v>
+        <v>5.893768125856658</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4975,22 +4975,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1566364298631881</v>
+        <v>0.1562785068747434</v>
       </c>
       <c r="C44">
-        <v>42.98911650873835</v>
+        <v>42.56681195700531</v>
       </c>
       <c r="D44">
-        <v>60.18529650873835</v>
+        <v>60.38028195700532</v>
       </c>
       <c r="E44">
-        <v>25.39718</v>
+        <v>26.01447</v>
       </c>
       <c r="F44">
-        <v>25.92618</v>
+        <v>26.54347</v>
       </c>
       <c r="G44">
         <v>8.73</v>
@@ -5011,28 +5011,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M44">
-        <v>1.433717754</v>
+        <v>1.467853891</v>
       </c>
       <c r="N44">
-        <v>7.016282245999999</v>
+        <v>6.982146108999999</v>
       </c>
       <c r="O44">
-        <v>1.7540705615</v>
+        <v>1.74553652725</v>
       </c>
       <c r="P44">
-        <v>5.2622116845</v>
+        <v>5.236609581749999</v>
       </c>
       <c r="Q44">
-        <v>5.192211684500001</v>
+        <v>5.16660958175</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2400291894192898</v>
+        <v>0.2428846611837604</v>
       </c>
       <c r="T44">
-        <v>1.878344707634631</v>
+        <v>1.905959301983861</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.893768125856659</v>
+        <v>5.756703750836736</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5057,22 +5057,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1562785068747434</v>
+        <v>0.1559205838862988</v>
       </c>
       <c r="C45">
-        <v>42.56681195700531</v>
+        <v>42.14577492078815</v>
       </c>
       <c r="D45">
-        <v>60.38028195700532</v>
+        <v>60.57653492078816</v>
       </c>
       <c r="E45">
-        <v>26.01447</v>
+        <v>26.63176</v>
       </c>
       <c r="F45">
-        <v>26.54347</v>
+        <v>27.16076</v>
       </c>
       <c r="G45">
         <v>8.73</v>
@@ -5093,28 +5093,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M45">
-        <v>1.467853891</v>
+        <v>1.501990028</v>
       </c>
       <c r="N45">
-        <v>6.982146108999999</v>
+        <v>6.948009971999999</v>
       </c>
       <c r="O45">
-        <v>1.74553652725</v>
+        <v>1.737002493</v>
       </c>
       <c r="P45">
-        <v>5.236609581749999</v>
+        <v>5.211007478999999</v>
       </c>
       <c r="Q45">
-        <v>5.16660958175</v>
+        <v>5.141007479000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2428846611837604</v>
+        <v>0.2458421140826764</v>
       </c>
       <c r="T45">
-        <v>1.905959301983861</v>
+        <v>1.934560131845564</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.756703750836736</v>
+        <v>5.625869574681357</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5139,22 +5139,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1559205838862988</v>
+        <v>0.1555626608978541</v>
       </c>
       <c r="C46">
-        <v>42.14577492078815</v>
+        <v>41.7260177997391</v>
       </c>
       <c r="D46">
-        <v>60.57653492078816</v>
+        <v>60.7740677997391</v>
       </c>
       <c r="E46">
-        <v>26.63176</v>
+        <v>27.24905</v>
       </c>
       <c r="F46">
-        <v>27.16076</v>
+        <v>27.77805</v>
       </c>
       <c r="G46">
         <v>8.73</v>
@@ -5175,28 +5175,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M46">
-        <v>1.501990028</v>
+        <v>1.536126165</v>
       </c>
       <c r="N46">
-        <v>6.948009971999999</v>
+        <v>6.913873834999999</v>
       </c>
       <c r="O46">
-        <v>1.737002493</v>
+        <v>1.72846845875</v>
       </c>
       <c r="P46">
-        <v>5.211007478999999</v>
+        <v>5.185405376249999</v>
       </c>
       <c r="Q46">
-        <v>5.141007479000001</v>
+        <v>5.115405376250001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2458421140826764</v>
+        <v>0.2489071107233711</v>
       </c>
       <c r="T46">
-        <v>1.934560131845564</v>
+        <v>1.964200991884056</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.625869574681357</v>
+        <v>5.500850250799548</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5221,22 +5221,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1555626608978541</v>
+        <v>0.1552047379094094</v>
       </c>
       <c r="C47">
-        <v>41.7260177997391</v>
+        <v>41.30755315577471</v>
       </c>
       <c r="D47">
-        <v>60.7740677997391</v>
+        <v>60.97289315577471</v>
       </c>
       <c r="E47">
-        <v>27.24905</v>
+        <v>27.86634</v>
       </c>
       <c r="F47">
-        <v>27.77805</v>
+        <v>28.39534</v>
       </c>
       <c r="G47">
         <v>8.73</v>
@@ -5257,28 +5257,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M47">
-        <v>1.536126165</v>
+        <v>1.570262302</v>
       </c>
       <c r="N47">
-        <v>6.913873834999999</v>
+        <v>6.879737697999999</v>
       </c>
       <c r="O47">
-        <v>1.72846845875</v>
+        <v>1.7199344245</v>
       </c>
       <c r="P47">
-        <v>5.185405376249999</v>
+        <v>5.159803273499999</v>
       </c>
       <c r="Q47">
-        <v>5.115405376250001</v>
+        <v>5.0898032735</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2489071107233711</v>
+        <v>0.2520856257581656</v>
       </c>
       <c r="T47">
-        <v>1.964200991884056</v>
+        <v>1.994939661553603</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.500850250799548</v>
+        <v>5.381266549695209</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5303,22 +5303,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1552047379094094</v>
+        <v>0.1548468149209647</v>
       </c>
       <c r="C48">
-        <v>41.30755315577471</v>
+        <v>40.89039371573882</v>
       </c>
       <c r="D48">
-        <v>60.97289315577471</v>
+        <v>61.17302371573882</v>
       </c>
       <c r="E48">
-        <v>27.86634</v>
+        <v>28.48363000000001</v>
       </c>
       <c r="F48">
-        <v>28.39534</v>
+        <v>29.01263000000001</v>
       </c>
       <c r="G48">
         <v>8.73</v>
@@ -5339,28 +5339,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M48">
-        <v>1.570262302</v>
+        <v>1.604398439</v>
       </c>
       <c r="N48">
-        <v>6.879737697999999</v>
+        <v>6.845601560999999</v>
       </c>
       <c r="O48">
-        <v>1.7199344245</v>
+        <v>1.71140039025</v>
       </c>
       <c r="P48">
-        <v>5.159803273499999</v>
+        <v>5.134201170749999</v>
       </c>
       <c r="Q48">
-        <v>5.0898032735</v>
+        <v>5.064201170750001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2520856257581656</v>
+        <v>0.2553840847565373</v>
       </c>
       <c r="T48">
-        <v>1.994939661553603</v>
+        <v>2.026838281022</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.381266549695209</v>
+        <v>5.266771516722971</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5385,22 +5385,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1548468149209647</v>
+        <v>0.1544888919325201</v>
       </c>
       <c r="C49">
-        <v>40.89039371573882</v>
+        <v>40.47455237411803</v>
       </c>
       <c r="D49">
-        <v>61.17302371573882</v>
+        <v>61.37447237411804</v>
       </c>
       <c r="E49">
-        <v>28.48363000000001</v>
+        <v>29.10092000000001</v>
       </c>
       <c r="F49">
-        <v>29.01263000000001</v>
+        <v>29.62992000000001</v>
       </c>
       <c r="G49">
         <v>8.73</v>
@@ -5421,28 +5421,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M49">
-        <v>1.604398439</v>
+        <v>1.638534576</v>
       </c>
       <c r="N49">
-        <v>6.845601560999999</v>
+        <v>6.811465423999999</v>
       </c>
       <c r="O49">
-        <v>1.71140039025</v>
+        <v>1.702866356</v>
       </c>
       <c r="P49">
-        <v>5.134201170749999</v>
+        <v>5.108599067999999</v>
       </c>
       <c r="Q49">
-        <v>5.064201170750001</v>
+        <v>5.038599068000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2553840847565373</v>
+        <v>0.2588094075625387</v>
       </c>
       <c r="T49">
-        <v>2.026838281022</v>
+        <v>2.059963770469952</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.266771516722971</v>
+        <v>5.157047110124576</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5467,22 +5467,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1544888919325201</v>
+        <v>0.1541309689440754</v>
       </c>
       <c r="C50">
-        <v>40.47455237411803</v>
+        <v>40.06004219581151</v>
       </c>
       <c r="D50">
-        <v>61.37447237411804</v>
+        <v>61.57725219581151</v>
       </c>
       <c r="E50">
-        <v>29.10092</v>
+        <v>29.71821</v>
       </c>
       <c r="F50">
-        <v>29.62992</v>
+        <v>30.24721</v>
       </c>
       <c r="G50">
         <v>8.73</v>
@@ -5503,28 +5503,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M50">
-        <v>1.638534576</v>
+        <v>1.672670713</v>
       </c>
       <c r="N50">
-        <v>6.811465424</v>
+        <v>6.777329286999999</v>
       </c>
       <c r="O50">
-        <v>1.702866356</v>
+        <v>1.69433232175</v>
       </c>
       <c r="P50">
-        <v>5.108599068</v>
+        <v>5.082996965249999</v>
       </c>
       <c r="Q50">
-        <v>5.038599068000002</v>
+        <v>5.01299696525</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2588094075625387</v>
+        <v>0.2623690567530891</v>
       </c>
       <c r="T50">
-        <v>2.059963770469952</v>
+        <v>2.094388298719784</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.157047110124577</v>
+        <v>5.051801250734279</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5549,22 +5549,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1541309689440754</v>
+        <v>0.1537730459556308</v>
       </c>
       <c r="C51">
-        <v>40.06004219581151</v>
+        <v>39.64687641895505</v>
       </c>
       <c r="D51">
-        <v>61.57725219581151</v>
+        <v>61.78137641895506</v>
       </c>
       <c r="E51">
-        <v>29.71821</v>
+        <v>30.3355</v>
       </c>
       <c r="F51">
-        <v>30.24721</v>
+        <v>30.8645</v>
       </c>
       <c r="G51">
         <v>8.73</v>
@@ -5585,28 +5585,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M51">
-        <v>1.672670713</v>
+        <v>1.70680685</v>
       </c>
       <c r="N51">
-        <v>6.777329286999999</v>
+        <v>6.743193149999999</v>
       </c>
       <c r="O51">
-        <v>1.69433232175</v>
+        <v>1.6857982875</v>
       </c>
       <c r="P51">
-        <v>5.082996965249999</v>
+        <v>5.057394862499999</v>
       </c>
       <c r="Q51">
-        <v>5.01299696525</v>
+        <v>4.9873948625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2623690567530891</v>
+        <v>0.2660710919112616</v>
       </c>
       <c r="T51">
-        <v>2.094388298719784</v>
+        <v>2.13018980809961</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.051801250734279</v>
+        <v>4.950765225719593</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1537730459556308</v>
+        <v>0.1534151229671862</v>
       </c>
       <c r="C52">
-        <v>39.64687641895505</v>
+        <v>39.2350684578023</v>
       </c>
       <c r="D52">
-        <v>61.78137641895506</v>
+        <v>61.9868584578023</v>
       </c>
       <c r="E52">
-        <v>30.3355</v>
+        <v>30.95279</v>
       </c>
       <c r="F52">
-        <v>30.8645</v>
+        <v>31.48179</v>
       </c>
       <c r="G52">
         <v>8.73</v>
@@ -5667,28 +5667,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M52">
-        <v>1.70680685</v>
+        <v>1.740942987</v>
       </c>
       <c r="N52">
-        <v>6.743193149999999</v>
+        <v>6.709057012999999</v>
       </c>
       <c r="O52">
-        <v>1.6857982875</v>
+        <v>1.67726425325</v>
       </c>
       <c r="P52">
-        <v>5.057394862499999</v>
+        <v>5.031792759749999</v>
       </c>
       <c r="Q52">
-        <v>4.9873948625</v>
+        <v>4.961792759750001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2660710919112616</v>
+        <v>0.2699242305452779</v>
       </c>
       <c r="T52">
-        <v>2.13018980809961</v>
+        <v>2.167452603576571</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.950765225719593</v>
+        <v>4.853691397764307</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5713,22 +5713,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1534151229671862</v>
+        <v>0.1530571999787415</v>
       </c>
       <c r="C53">
-        <v>39.2350684578023</v>
+        <v>38.82463190566326</v>
       </c>
       <c r="D53">
-        <v>61.9868584578023</v>
+        <v>62.19371190566327</v>
       </c>
       <c r="E53">
-        <v>30.95279</v>
+        <v>31.57008000000001</v>
       </c>
       <c r="F53">
-        <v>31.48179</v>
+        <v>32.09908000000001</v>
       </c>
       <c r="G53">
         <v>8.73</v>
@@ -5749,28 +5749,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M53">
-        <v>1.740942987</v>
+        <v>1.775079124000001</v>
       </c>
       <c r="N53">
-        <v>6.709057012999999</v>
+        <v>6.674920875999999</v>
       </c>
       <c r="O53">
-        <v>1.67726425325</v>
+        <v>1.668730219</v>
       </c>
       <c r="P53">
-        <v>5.031792759749999</v>
+        <v>5.006190656999999</v>
       </c>
       <c r="Q53">
-        <v>4.961792759750001</v>
+        <v>4.936190657000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2699242305452779</v>
+        <v>0.273937916622378</v>
       </c>
       <c r="T53">
-        <v>2.167452603576571</v>
+        <v>2.206268015531739</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.853691397764307</v>
+        <v>4.760351178576531</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1530571999787415</v>
+        <v>0.1526992769902968</v>
       </c>
       <c r="C54">
-        <v>38.82463190566326</v>
+        <v>38.41558053790173</v>
       </c>
       <c r="D54">
-        <v>62.19371190566327</v>
+        <v>62.40195053790173</v>
       </c>
       <c r="E54">
-        <v>31.57008000000001</v>
+        <v>32.18737</v>
       </c>
       <c r="F54">
-        <v>32.09908000000001</v>
+        <v>32.71637</v>
       </c>
       <c r="G54">
         <v>8.73</v>
@@ -5831,28 +5831,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M54">
-        <v>1.775079124000001</v>
+        <v>1.809215261</v>
       </c>
       <c r="N54">
-        <v>6.674920875999999</v>
+        <v>6.640784738999999</v>
       </c>
       <c r="O54">
-        <v>1.668730219</v>
+        <v>1.66019618475</v>
       </c>
       <c r="P54">
-        <v>5.006190656999999</v>
+        <v>4.98058855425</v>
       </c>
       <c r="Q54">
-        <v>4.936190657000001</v>
+        <v>4.910588554250001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.273937916622378</v>
+        <v>0.2781223978516953</v>
       </c>
       <c r="T54">
-        <v>2.206268015531739</v>
+        <v>2.246735147144574</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.760351178576531</v>
+        <v>4.670533231810937</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1526992769902968</v>
+        <v>0.1523413540018521</v>
       </c>
       <c r="C55">
-        <v>38.41558053790173</v>
+        <v>38.00792831499356</v>
       </c>
       <c r="D55">
-        <v>62.40195053790173</v>
+        <v>62.61158831499358</v>
       </c>
       <c r="E55">
-        <v>32.18737</v>
+        <v>32.80466000000001</v>
       </c>
       <c r="F55">
-        <v>32.71637</v>
+        <v>33.33366000000001</v>
       </c>
       <c r="G55">
         <v>8.73</v>
@@ -5913,28 +5913,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M55">
-        <v>1.809215261</v>
+        <v>1.843351398</v>
       </c>
       <c r="N55">
-        <v>6.640784738999999</v>
+        <v>6.606648601999999</v>
       </c>
       <c r="O55">
-        <v>1.66019618475</v>
+        <v>1.6516621505</v>
       </c>
       <c r="P55">
-        <v>4.98058855425</v>
+        <v>4.954986451499999</v>
       </c>
       <c r="Q55">
-        <v>4.910588554250001</v>
+        <v>4.884986451500001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2781223978516953</v>
+        <v>0.2824888130475047</v>
       </c>
       <c r="T55">
-        <v>2.246735147144574</v>
+        <v>2.288961719262314</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.670533231810937</v>
+        <v>4.58404187566629</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5959,22 +5959,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1523413540018521</v>
+        <v>0.1519834310134075</v>
       </c>
       <c r="C56">
-        <v>38.00792831499356</v>
+        <v>37.60168938564635</v>
       </c>
       <c r="D56">
-        <v>62.61158831499358</v>
+        <v>62.82263938564635</v>
       </c>
       <c r="E56">
-        <v>32.80466000000001</v>
+        <v>33.42195</v>
       </c>
       <c r="F56">
-        <v>33.33366000000001</v>
+        <v>33.95095000000001</v>
       </c>
       <c r="G56">
         <v>8.73</v>
@@ -5995,28 +5995,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M56">
-        <v>1.843351398</v>
+        <v>1.877487535</v>
       </c>
       <c r="N56">
-        <v>6.606648601999999</v>
+        <v>6.572512464999999</v>
       </c>
       <c r="O56">
-        <v>1.6516621505</v>
+        <v>1.64312811625</v>
       </c>
       <c r="P56">
-        <v>4.954986451499999</v>
+        <v>4.929384348749999</v>
       </c>
       <c r="Q56">
-        <v>4.884986451500001</v>
+        <v>4.859384348750001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2824888130475047</v>
+        <v>0.2870492911409056</v>
       </c>
       <c r="T56">
-        <v>2.288961719262314</v>
+        <v>2.333065027918621</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.58404187566629</v>
+        <v>4.500695659745085</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6041,22 +6041,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1519834310134075</v>
+        <v>0.1526755080249628</v>
       </c>
       <c r="C57">
-        <v>37.60168938564635</v>
+        <v>36.57758864549175</v>
       </c>
       <c r="D57">
-        <v>62.82263938564635</v>
+        <v>62.41582864549176</v>
       </c>
       <c r="E57">
-        <v>33.42195</v>
+        <v>34.03924000000001</v>
       </c>
       <c r="F57">
-        <v>33.95095000000001</v>
+        <v>34.56824000000001</v>
       </c>
       <c r="G57">
         <v>8.73</v>
@@ -6077,45 +6077,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M57">
-        <v>1.877487535</v>
+        <v>1.998044272000001</v>
       </c>
       <c r="N57">
-        <v>6.572512464999999</v>
+        <v>6.451955727999999</v>
       </c>
       <c r="O57">
-        <v>1.64312811625</v>
+        <v>1.612988932</v>
       </c>
       <c r="P57">
-        <v>4.929384348749999</v>
+        <v>4.838966795999999</v>
       </c>
       <c r="Q57">
-        <v>4.859384348750001</v>
+        <v>4.768966796000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2870492911409056</v>
+        <v>0.2918170636930973</v>
       </c>
       <c r="T57">
-        <v>2.333065027918621</v>
+        <v>2.379173032422941</v>
       </c>
       <c r="U57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.500695659745085</v>
+        <v>4.229135519375517</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6123,22 +6123,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1526755080249628</v>
+        <v>0.1523363350365182</v>
       </c>
       <c r="C58">
-        <v>36.57758864549175</v>
+        <v>36.15900796959873</v>
       </c>
       <c r="D58">
-        <v>62.41582864549176</v>
+        <v>62.61453796959873</v>
       </c>
       <c r="E58">
-        <v>34.03924000000001</v>
+        <v>34.65653</v>
       </c>
       <c r="F58">
-        <v>34.56824000000001</v>
+        <v>35.18553000000001</v>
       </c>
       <c r="G58">
         <v>8.73</v>
@@ -6159,28 +6159,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M58">
-        <v>1.998044272000001</v>
+        <v>2.033723634000001</v>
       </c>
       <c r="N58">
-        <v>6.451955727999999</v>
+        <v>6.416276365999998</v>
       </c>
       <c r="O58">
-        <v>1.612988932</v>
+        <v>1.6040690915</v>
       </c>
       <c r="P58">
-        <v>4.838966795999999</v>
+        <v>4.812207274499999</v>
       </c>
       <c r="Q58">
-        <v>4.768966796000001</v>
+        <v>4.7422072745</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2918170636930973</v>
+        <v>0.2968065931081819</v>
       </c>
       <c r="T58">
-        <v>2.379173032422941</v>
+        <v>2.4274255952763</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.229135519375517</v>
+        <v>4.154940159386472</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6205,22 +6205,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1523363350365182</v>
+        <v>0.1519971620480735</v>
       </c>
       <c r="C59">
-        <v>36.15900796959873</v>
+        <v>35.74169657122667</v>
       </c>
       <c r="D59">
-        <v>62.61453796959873</v>
+        <v>62.81451657122668</v>
       </c>
       <c r="E59">
-        <v>34.65653</v>
+        <v>35.27382000000001</v>
       </c>
       <c r="F59">
-        <v>35.18553000000001</v>
+        <v>35.80282000000001</v>
       </c>
       <c r="G59">
         <v>8.73</v>
@@ -6241,28 +6241,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M59">
-        <v>2.033723634000001</v>
+        <v>2.069402996000001</v>
       </c>
       <c r="N59">
-        <v>6.416276365999998</v>
+        <v>6.380597003999998</v>
       </c>
       <c r="O59">
-        <v>1.6040690915</v>
+        <v>1.595149251</v>
       </c>
       <c r="P59">
-        <v>4.812207274499999</v>
+        <v>4.785447752999999</v>
       </c>
       <c r="Q59">
-        <v>4.7422072745</v>
+        <v>4.715447753</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2968065931081819</v>
+        <v>0.3020337191620798</v>
       </c>
       <c r="T59">
-        <v>2.4274255952763</v>
+        <v>2.477975899217914</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.154940159386472</v>
+        <v>4.083303260086705</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6287,22 +6287,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1519971620480735</v>
+        <v>0.1516579890596289</v>
       </c>
       <c r="C60">
-        <v>35.74169657122668</v>
+        <v>35.32566665081468</v>
       </c>
       <c r="D60">
-        <v>62.81451657122668</v>
+        <v>63.01577665081468</v>
       </c>
       <c r="E60">
-        <v>35.27382</v>
+        <v>35.89111</v>
       </c>
       <c r="F60">
-        <v>35.80282</v>
+        <v>36.42011</v>
       </c>
       <c r="G60">
         <v>8.73</v>
@@ -6323,28 +6323,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M60">
-        <v>2.069402996</v>
+        <v>2.105082358</v>
       </c>
       <c r="N60">
-        <v>6.380597003999998</v>
+        <v>6.344917641999999</v>
       </c>
       <c r="O60">
-        <v>1.595149251</v>
+        <v>1.5862294105</v>
       </c>
       <c r="P60">
-        <v>4.785447752999999</v>
+        <v>4.758688231499999</v>
       </c>
       <c r="Q60">
-        <v>4.715447753</v>
+        <v>4.6886882315</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3020337191620798</v>
+        <v>0.3075158269747045</v>
       </c>
       <c r="T60">
-        <v>2.477975899217913</v>
+        <v>2.530992071644484</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.083303260086707</v>
+        <v>4.014094730254729</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6369,22 +6369,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1516579890596289</v>
+        <v>0.1528938160711842</v>
       </c>
       <c r="C61">
-        <v>35.32566665081468</v>
+        <v>33.981195551138</v>
       </c>
       <c r="D61">
-        <v>63.01577665081468</v>
+        <v>62.28859555113801</v>
       </c>
       <c r="E61">
-        <v>35.89111</v>
+        <v>36.5084</v>
       </c>
       <c r="F61">
-        <v>36.42011</v>
+        <v>37.03740000000001</v>
       </c>
       <c r="G61">
         <v>8.73</v>
@@ -6405,45 +6405,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M61">
-        <v>2.105082358</v>
+        <v>2.27039262</v>
       </c>
       <c r="N61">
-        <v>6.344917641999999</v>
+        <v>6.179607379999998</v>
       </c>
       <c r="O61">
-        <v>1.5862294105</v>
+        <v>1.544901845</v>
       </c>
       <c r="P61">
-        <v>4.758688231499999</v>
+        <v>4.634705534999998</v>
       </c>
       <c r="Q61">
-        <v>4.6886882315</v>
+        <v>4.564705535</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3075158269747045</v>
+        <v>0.3132720401779605</v>
       </c>
       <c r="T61">
-        <v>2.530992071644484</v>
+        <v>2.586659052692383</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.014094730254729</v>
+        <v>3.721823232494474</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6451,22 +6451,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1528938160711842</v>
+        <v>0.1525808930827395</v>
       </c>
       <c r="C62">
-        <v>33.981195551138</v>
+        <v>33.5464432028018</v>
       </c>
       <c r="D62">
-        <v>62.28859555113801</v>
+        <v>62.47113320280179</v>
       </c>
       <c r="E62">
-        <v>36.5084</v>
+        <v>37.12569</v>
       </c>
       <c r="F62">
-        <v>37.03740000000001</v>
+        <v>37.65469</v>
       </c>
       <c r="G62">
         <v>8.73</v>
@@ -6487,28 +6487,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M62">
-        <v>2.27039262</v>
+        <v>2.308232497</v>
       </c>
       <c r="N62">
-        <v>6.179607379999998</v>
+        <v>6.141767502999999</v>
       </c>
       <c r="O62">
-        <v>1.544901845</v>
+        <v>1.53544187575</v>
       </c>
       <c r="P62">
-        <v>4.634705534999998</v>
+        <v>4.606325627249999</v>
       </c>
       <c r="Q62">
-        <v>4.564705535</v>
+        <v>4.536325627250001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3132720401779605</v>
+        <v>0.3193234438018963</v>
       </c>
       <c r="T62">
-        <v>2.586659052692383</v>
+        <v>2.645180750717098</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.721823232494474</v>
+        <v>3.660809736879811</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6533,22 +6533,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1525808930827395</v>
+        <v>0.1522679700942949</v>
       </c>
       <c r="C63">
-        <v>33.5464432028018</v>
+        <v>33.11276385749945</v>
       </c>
       <c r="D63">
-        <v>62.47113320280179</v>
+        <v>62.65474385749946</v>
       </c>
       <c r="E63">
-        <v>37.12569</v>
+        <v>37.74298</v>
       </c>
       <c r="F63">
-        <v>37.65469</v>
+        <v>38.27198000000001</v>
       </c>
       <c r="G63">
         <v>8.73</v>
@@ -6569,28 +6569,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M63">
-        <v>2.308232497</v>
+        <v>2.346072374</v>
       </c>
       <c r="N63">
-        <v>6.141767502999999</v>
+        <v>6.103927625999999</v>
       </c>
       <c r="O63">
-        <v>1.53544187575</v>
+        <v>1.5259819065</v>
       </c>
       <c r="P63">
-        <v>4.606325627249999</v>
+        <v>4.577945719499999</v>
       </c>
       <c r="Q63">
-        <v>4.536325627250001</v>
+        <v>4.5079457195</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3193234438018963</v>
+        <v>0.3256933423534076</v>
       </c>
       <c r="T63">
-        <v>2.645180750717098</v>
+        <v>2.706782538111534</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.660809736879811</v>
+        <v>3.60176441854304</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6615,22 +6615,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1522679700942949</v>
+        <v>0.1519550471058502</v>
       </c>
       <c r="C64">
-        <v>33.11276385749945</v>
+        <v>32.68016700419999</v>
       </c>
       <c r="D64">
-        <v>62.65474385749946</v>
+        <v>62.83943700419999</v>
       </c>
       <c r="E64">
-        <v>37.74298</v>
+        <v>38.36027</v>
       </c>
       <c r="F64">
-        <v>38.27198000000001</v>
+        <v>38.88927</v>
       </c>
       <c r="G64">
         <v>8.73</v>
@@ -6651,28 +6651,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M64">
-        <v>2.346072374</v>
+        <v>2.383912251</v>
       </c>
       <c r="N64">
-        <v>6.103927625999999</v>
+        <v>6.066087748999999</v>
       </c>
       <c r="O64">
-        <v>1.5259819065</v>
+        <v>1.51652193725</v>
       </c>
       <c r="P64">
-        <v>4.577945719499999</v>
+        <v>4.54956581175</v>
       </c>
       <c r="Q64">
-        <v>4.5079457195</v>
+        <v>4.479565811750001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3256933423534076</v>
+        <v>0.3324075597455411</v>
       </c>
       <c r="T64">
-        <v>2.706782538111534</v>
+        <v>2.771714151851616</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.60176441854304</v>
+        <v>3.544593554756642</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6697,22 +6697,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1519550471058502</v>
+        <v>0.1529861241174056</v>
       </c>
       <c r="C65">
-        <v>32.68016700419999</v>
+        <v>31.45839298681783</v>
       </c>
       <c r="D65">
-        <v>62.83943700419999</v>
+        <v>62.23495298681784</v>
       </c>
       <c r="E65">
-        <v>38.36027</v>
+        <v>38.97756</v>
       </c>
       <c r="F65">
-        <v>38.88927</v>
+        <v>39.50656000000001</v>
       </c>
       <c r="G65">
         <v>8.73</v>
@@ -6733,45 +6733,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M65">
-        <v>2.383912251</v>
+        <v>2.532370496000001</v>
       </c>
       <c r="N65">
-        <v>6.066087748999999</v>
+        <v>5.917629503999999</v>
       </c>
       <c r="O65">
-        <v>1.51652193725</v>
+        <v>1.479407376</v>
       </c>
       <c r="P65">
-        <v>4.54956581175</v>
+        <v>4.438222128</v>
       </c>
       <c r="Q65">
-        <v>4.479565811750001</v>
+        <v>4.368222128000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3324075597455411</v>
+        <v>0.3394947892150155</v>
       </c>
       <c r="T65">
-        <v>2.771714151851616</v>
+        <v>2.840253077466147</v>
       </c>
       <c r="U65">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.544593554756642</v>
+        <v>3.336794522502602</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1529861241174056</v>
+        <v>0.1526942011289609</v>
       </c>
       <c r="C66">
-        <v>31.45839298681783</v>
+        <v>31.01106368879928</v>
       </c>
       <c r="D66">
-        <v>62.23495298681784</v>
+        <v>62.40491368879929</v>
       </c>
       <c r="E66">
-        <v>38.97756</v>
+        <v>39.59485</v>
       </c>
       <c r="F66">
-        <v>39.50656000000001</v>
+        <v>40.12385</v>
       </c>
       <c r="G66">
         <v>8.73</v>
@@ -6815,28 +6815,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M66">
-        <v>2.532370496000001</v>
+        <v>2.571938785</v>
       </c>
       <c r="N66">
-        <v>5.917629503999999</v>
+        <v>5.878061214999999</v>
       </c>
       <c r="O66">
-        <v>1.479407376</v>
+        <v>1.46951530375</v>
       </c>
       <c r="P66">
-        <v>4.438222128</v>
+        <v>4.408545911249999</v>
       </c>
       <c r="Q66">
-        <v>4.368222128000001</v>
+        <v>4.338545911250001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3394947892150155</v>
+        <v>0.3469870032256027</v>
       </c>
       <c r="T66">
-        <v>2.840253077466147</v>
+        <v>2.912708513115794</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.336794522502602</v>
+        <v>3.285459222156408</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6861,22 +6861,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1526942011289609</v>
+        <v>0.1524022781405163</v>
       </c>
       <c r="C67">
-        <v>31.01106368879928</v>
+        <v>30.56466524210786</v>
       </c>
       <c r="D67">
-        <v>62.40491368879929</v>
+        <v>62.57580524210786</v>
       </c>
       <c r="E67">
-        <v>39.59485</v>
+        <v>40.21214000000001</v>
       </c>
       <c r="F67">
-        <v>40.12385</v>
+        <v>40.74114000000001</v>
       </c>
       <c r="G67">
         <v>8.73</v>
@@ -6897,28 +6897,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M67">
-        <v>2.571938785</v>
+        <v>2.611507074000001</v>
       </c>
       <c r="N67">
-        <v>5.878061214999999</v>
+        <v>5.838492925999999</v>
       </c>
       <c r="O67">
-        <v>1.46951530375</v>
+        <v>1.4596232315</v>
       </c>
       <c r="P67">
-        <v>4.408545911249999</v>
+        <v>4.378869694499999</v>
       </c>
       <c r="Q67">
-        <v>4.338545911250001</v>
+        <v>4.3088696945</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3469870032256027</v>
+        <v>0.3549199357074008</v>
       </c>
       <c r="T67">
-        <v>2.912708513115794</v>
+        <v>2.989426033215419</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.285459222156408</v>
+        <v>3.23567953697222</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1524022781405163</v>
+        <v>0.1521103551520716</v>
       </c>
       <c r="C68">
-        <v>30.56466524210786</v>
+        <v>30.11920531495895</v>
       </c>
       <c r="D68">
-        <v>62.57580524210786</v>
+        <v>62.74763531495896</v>
       </c>
       <c r="E68">
-        <v>40.21214000000001</v>
+        <v>40.82943</v>
       </c>
       <c r="F68">
-        <v>40.74114000000001</v>
+        <v>41.35843000000001</v>
       </c>
       <c r="G68">
         <v>8.73</v>
@@ -6979,28 +6979,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M68">
-        <v>2.611507074000001</v>
+        <v>2.651075363</v>
       </c>
       <c r="N68">
-        <v>5.838492925999999</v>
+        <v>5.798924636999999</v>
       </c>
       <c r="O68">
-        <v>1.4596232315</v>
+        <v>1.44973115925</v>
       </c>
       <c r="P68">
-        <v>4.378869694499999</v>
+        <v>4.349193477749999</v>
       </c>
       <c r="Q68">
-        <v>4.3088696945</v>
+        <v>4.279193477750001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3549199357074008</v>
+        <v>0.3633336519759746</v>
       </c>
       <c r="T68">
-        <v>2.989426033215419</v>
+        <v>3.07079309998775</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.23567953697222</v>
+        <v>3.187385812539799</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7025,22 +7025,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1521103551520716</v>
+        <v>0.1518184321636269</v>
       </c>
       <c r="C69">
-        <v>30.11920531495895</v>
+        <v>29.6746916600261</v>
       </c>
       <c r="D69">
-        <v>62.74763531495896</v>
+        <v>62.92041166002611</v>
       </c>
       <c r="E69">
-        <v>40.82943</v>
+        <v>41.44672000000001</v>
       </c>
       <c r="F69">
-        <v>41.35843000000001</v>
+        <v>41.97572000000001</v>
       </c>
       <c r="G69">
         <v>8.73</v>
@@ -7061,28 +7061,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M69">
-        <v>2.651075363</v>
+        <v>2.690643652000001</v>
       </c>
       <c r="N69">
-        <v>5.798924636999999</v>
+        <v>5.759356347999999</v>
       </c>
       <c r="O69">
-        <v>1.44973115925</v>
+        <v>1.439839087</v>
       </c>
       <c r="P69">
-        <v>4.349193477749999</v>
+        <v>4.319517261</v>
       </c>
       <c r="Q69">
-        <v>4.279193477750001</v>
+        <v>4.249517261000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3633336519759746</v>
+        <v>0.3722732255113342</v>
       </c>
       <c r="T69">
-        <v>3.07079309998775</v>
+        <v>3.157245608433351</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.187385812539799</v>
+        <v>3.140512491767155</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7107,22 +7107,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1518184321636269</v>
+        <v>0.1515265091751823</v>
       </c>
       <c r="C70">
-        <v>29.6746916600261</v>
+        <v>29.2311321156068</v>
       </c>
       <c r="D70">
-        <v>62.92041166002611</v>
+        <v>63.09414211560681</v>
       </c>
       <c r="E70">
-        <v>41.44672000000001</v>
+        <v>42.06401</v>
       </c>
       <c r="F70">
-        <v>41.97572000000001</v>
+        <v>42.59301000000001</v>
       </c>
       <c r="G70">
         <v>8.73</v>
@@ -7143,28 +7143,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M70">
-        <v>2.690643652000001</v>
+        <v>2.730211941000001</v>
       </c>
       <c r="N70">
-        <v>5.759356347999999</v>
+        <v>5.719788058999999</v>
       </c>
       <c r="O70">
-        <v>1.439839087</v>
+        <v>1.42994701475</v>
       </c>
       <c r="P70">
-        <v>4.319517261</v>
+        <v>4.289841044249999</v>
       </c>
       <c r="Q70">
-        <v>4.249517261000001</v>
+        <v>4.219841044250001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3722732255113342</v>
+        <v>0.3817895457263945</v>
       </c>
       <c r="T70">
-        <v>3.157245608433351</v>
+        <v>3.249275698068991</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.140512491767155</v>
+        <v>3.094997817973428</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7189,22 +7189,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1515265091751823</v>
+        <v>0.1512345861867376</v>
       </c>
       <c r="C71">
-        <v>29.2311321156068</v>
+        <v>28.78853460680811</v>
       </c>
       <c r="D71">
-        <v>63.09414211560681</v>
+        <v>63.26883460680811</v>
       </c>
       <c r="E71">
-        <v>42.06401</v>
+        <v>42.68130000000001</v>
       </c>
       <c r="F71">
-        <v>42.59301000000001</v>
+        <v>43.21030000000001</v>
       </c>
       <c r="G71">
         <v>8.73</v>
@@ -7225,28 +7225,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M71">
-        <v>2.730211941000001</v>
+        <v>2.769780230000001</v>
       </c>
       <c r="N71">
-        <v>5.719788058999999</v>
+        <v>5.680219769999999</v>
       </c>
       <c r="O71">
-        <v>1.42994701475</v>
+        <v>1.4200549425</v>
       </c>
       <c r="P71">
-        <v>4.289841044249999</v>
+        <v>4.260164827499999</v>
       </c>
       <c r="Q71">
-        <v>4.219841044250001</v>
+        <v>4.1901648275</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3817895457263945</v>
+        <v>0.3919402872891254</v>
       </c>
       <c r="T71">
-        <v>3.249275698068991</v>
+        <v>3.347441127013673</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.094997817973428</v>
+        <v>3.05078356343095</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7271,22 +7271,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1512345861867376</v>
+        <v>0.150942663198293</v>
       </c>
       <c r="C72">
-        <v>28.78853460680811</v>
+        <v>28.34690714675155</v>
       </c>
       <c r="D72">
-        <v>63.26883460680811</v>
+        <v>63.44449714675156</v>
       </c>
       <c r="E72">
-        <v>42.68130000000001</v>
+        <v>43.29859</v>
       </c>
       <c r="F72">
-        <v>43.21030000000001</v>
+        <v>43.82759000000001</v>
       </c>
       <c r="G72">
         <v>8.73</v>
@@ -7307,28 +7307,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M72">
-        <v>2.769780230000001</v>
+        <v>2.809348519000001</v>
       </c>
       <c r="N72">
-        <v>5.680219769999999</v>
+        <v>5.640651480999999</v>
       </c>
       <c r="O72">
-        <v>1.4200549425</v>
+        <v>1.41016287025</v>
       </c>
       <c r="P72">
-        <v>4.260164827499999</v>
+        <v>4.230488610749999</v>
       </c>
       <c r="Q72">
-        <v>4.1901648275</v>
+        <v>4.160488610750001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3919402872891254</v>
+        <v>0.4027910799941138</v>
       </c>
       <c r="T72">
-        <v>3.347441127013673</v>
+        <v>3.452376585540748</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.05078356343095</v>
+        <v>3.007814780847416</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7353,22 +7353,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.150942663198293</v>
+        <v>0.1548627402098483</v>
       </c>
       <c r="C73">
-        <v>28.34690714675156</v>
+        <v>25.44921126023036</v>
       </c>
       <c r="D73">
-        <v>63.44449714675156</v>
+        <v>61.16409126023037</v>
       </c>
       <c r="E73">
-        <v>43.29859</v>
+        <v>43.91588</v>
       </c>
       <c r="F73">
-        <v>43.82759</v>
+        <v>44.44488</v>
       </c>
       <c r="G73">
         <v>8.73</v>
@@ -7389,45 +7389,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M73">
-        <v>2.809348519</v>
+        <v>3.195586872000001</v>
       </c>
       <c r="N73">
-        <v>5.640651480999999</v>
+        <v>5.254413127999999</v>
       </c>
       <c r="O73">
-        <v>1.41016287025</v>
+        <v>1.313603282</v>
       </c>
       <c r="P73">
-        <v>4.230488610749999</v>
+        <v>3.940809845999999</v>
       </c>
       <c r="Q73">
-        <v>4.160488610750001</v>
+        <v>3.870809846</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4027910799941136</v>
+        <v>0.4144169293208867</v>
       </c>
       <c r="T73">
-        <v>3.452376585540747</v>
+        <v>3.564807433962612</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.007814780847416</v>
+        <v>2.644271721742133</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7435,22 +7435,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1548627402098483</v>
+        <v>0.1546293172214036</v>
       </c>
       <c r="C74">
-        <v>25.44921126023036</v>
+        <v>24.96310930157791</v>
       </c>
       <c r="D74">
-        <v>61.16409126023037</v>
+        <v>61.29527930157791</v>
       </c>
       <c r="E74">
-        <v>43.91588</v>
+        <v>44.53317</v>
       </c>
       <c r="F74">
-        <v>44.44488</v>
+        <v>45.06217</v>
       </c>
       <c r="G74">
         <v>8.73</v>
@@ -7471,28 +7471,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M74">
-        <v>3.195586872000001</v>
+        <v>3.239970023000001</v>
       </c>
       <c r="N74">
-        <v>5.254413127999999</v>
+        <v>5.210029976999999</v>
       </c>
       <c r="O74">
-        <v>1.313603282</v>
+        <v>1.30250749425</v>
       </c>
       <c r="P74">
-        <v>3.940809845999999</v>
+        <v>3.907522482749999</v>
       </c>
       <c r="Q74">
-        <v>3.870809846</v>
+        <v>3.837522482750001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4144169293208867</v>
+        <v>0.4269039526718653</v>
       </c>
       <c r="T74">
-        <v>3.564807433962612</v>
+        <v>3.68556649337869</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.644271721742133</v>
+        <v>2.608048821444296</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7517,22 +7517,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1546293172214036</v>
+        <v>0.154395894232959</v>
       </c>
       <c r="C75">
-        <v>24.96310930157791</v>
+        <v>24.47757131092581</v>
       </c>
       <c r="D75">
-        <v>61.29527930157791</v>
+        <v>61.42703131092582</v>
       </c>
       <c r="E75">
-        <v>44.53317</v>
+        <v>45.15046</v>
       </c>
       <c r="F75">
-        <v>45.06217</v>
+        <v>45.67946000000001</v>
       </c>
       <c r="G75">
         <v>8.73</v>
@@ -7553,28 +7553,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M75">
-        <v>3.239970023000001</v>
+        <v>3.284353174</v>
       </c>
       <c r="N75">
-        <v>5.210029976999999</v>
+        <v>5.165646825999999</v>
       </c>
       <c r="O75">
-        <v>1.30250749425</v>
+        <v>1.2914117065</v>
       </c>
       <c r="P75">
-        <v>3.907522482749999</v>
+        <v>3.874235119499999</v>
       </c>
       <c r="Q75">
-        <v>3.837522482750001</v>
+        <v>3.8042351195</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4269039526718653</v>
+        <v>0.4403515162806114</v>
       </c>
       <c r="T75">
-        <v>3.68556649337869</v>
+        <v>3.815614711211389</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.608048821444296</v>
+        <v>2.572804918451805</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7599,22 +7599,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.154395894232959</v>
+        <v>0.1541624712445143</v>
       </c>
       <c r="C76">
-        <v>24.47757131092581</v>
+        <v>23.99260093279494</v>
       </c>
       <c r="D76">
-        <v>61.42703131092582</v>
+        <v>61.55935093279494</v>
       </c>
       <c r="E76">
-        <v>45.15046</v>
+        <v>45.76775</v>
       </c>
       <c r="F76">
-        <v>45.67946000000001</v>
+        <v>46.29675</v>
       </c>
       <c r="G76">
         <v>8.73</v>
@@ -7635,28 +7635,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M76">
-        <v>3.284353174</v>
+        <v>3.328736325</v>
       </c>
       <c r="N76">
-        <v>5.165646825999999</v>
+        <v>5.121263674999999</v>
       </c>
       <c r="O76">
-        <v>1.2914117065</v>
+        <v>1.28031591875</v>
       </c>
       <c r="P76">
-        <v>3.874235119499999</v>
+        <v>3.840947756249999</v>
       </c>
       <c r="Q76">
-        <v>3.8042351195</v>
+        <v>3.770947756250001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4403515162806114</v>
+        <v>0.4548748849780572</v>
       </c>
       <c r="T76">
-        <v>3.815614711211389</v>
+        <v>3.956066786470704</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.572804918451805</v>
+        <v>2.538500852872448</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7681,22 +7681,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1541624712445143</v>
+        <v>0.1539290482560697</v>
       </c>
       <c r="C77">
-        <v>23.99260093279494</v>
+        <v>23.50820184317656</v>
       </c>
       <c r="D77">
-        <v>61.55935093279494</v>
+        <v>61.69224184317657</v>
       </c>
       <c r="E77">
-        <v>45.76775</v>
+        <v>46.38504</v>
       </c>
       <c r="F77">
-        <v>46.29675</v>
+        <v>46.91404000000001</v>
       </c>
       <c r="G77">
         <v>8.73</v>
@@ -7717,28 +7717,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M77">
-        <v>3.328736325</v>
+        <v>3.373119476000001</v>
       </c>
       <c r="N77">
-        <v>5.121263674999999</v>
+        <v>5.076880523999998</v>
       </c>
       <c r="O77">
-        <v>1.28031591875</v>
+        <v>1.269220131</v>
       </c>
       <c r="P77">
-        <v>3.840947756249999</v>
+        <v>3.807660392999999</v>
       </c>
       <c r="Q77">
-        <v>3.770947756250001</v>
+        <v>3.737660393</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4548748849780572</v>
+        <v>0.4706085344002902</v>
       </c>
       <c r="T77">
-        <v>3.956066786470704</v>
+        <v>4.108223201334962</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.538500852872448</v>
+        <v>2.505099525860968</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7763,22 +7763,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1539290482560697</v>
+        <v>0.155947875267625</v>
       </c>
       <c r="C78">
-        <v>23.50820184317656</v>
+        <v>21.76019584948352</v>
       </c>
       <c r="D78">
-        <v>61.69224184317657</v>
+        <v>60.56152584948352</v>
       </c>
       <c r="E78">
-        <v>46.38504</v>
+        <v>47.00233</v>
       </c>
       <c r="F78">
-        <v>46.91404000000001</v>
+        <v>47.53133</v>
       </c>
       <c r="G78">
         <v>8.73</v>
@@ -7799,45 +7799,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M78">
-        <v>3.373119476000001</v>
+        <v>3.602874814000001</v>
       </c>
       <c r="N78">
-        <v>5.076880523999998</v>
+        <v>4.847125185999999</v>
       </c>
       <c r="O78">
-        <v>1.269220131</v>
+        <v>1.2117812965</v>
       </c>
       <c r="P78">
-        <v>3.807660392999999</v>
+        <v>3.635343889499999</v>
       </c>
       <c r="Q78">
-        <v>3.737660393</v>
+        <v>3.5653438895</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4706085344002902</v>
+        <v>0.4877103272505435</v>
       </c>
       <c r="T78">
-        <v>4.108223201334962</v>
+        <v>4.273610608796112</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.505099525860968</v>
+        <v>2.34534932137112</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7845,22 +7845,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.155947875267625</v>
+        <v>0.1557437022791803</v>
       </c>
       <c r="C79">
-        <v>21.76019584948352</v>
+        <v>21.25537275264509</v>
       </c>
       <c r="D79">
-        <v>60.56152584948352</v>
+        <v>60.6739927526451</v>
       </c>
       <c r="E79">
-        <v>47.00233</v>
+        <v>47.61962</v>
       </c>
       <c r="F79">
-        <v>47.53133</v>
+        <v>48.14862000000001</v>
       </c>
       <c r="G79">
         <v>8.73</v>
@@ -7881,28 +7881,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M79">
-        <v>3.602874814000001</v>
+        <v>3.649665396000001</v>
       </c>
       <c r="N79">
-        <v>4.847125185999999</v>
+        <v>4.800334603999998</v>
       </c>
       <c r="O79">
-        <v>1.2117812965</v>
+        <v>1.200083650999999</v>
       </c>
       <c r="P79">
-        <v>3.635343889499999</v>
+        <v>3.600250952999998</v>
       </c>
       <c r="Q79">
-        <v>3.5653438895</v>
+        <v>3.530250953</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4877103272505435</v>
+        <v>0.5063668285417288</v>
       </c>
       <c r="T79">
-        <v>4.273610608796112</v>
+        <v>4.454033235117366</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.34534932137112</v>
+        <v>2.315280740327899</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7927,22 +7927,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1557437022791803</v>
+        <v>0.1555395292907357</v>
       </c>
       <c r="C80">
-        <v>21.25537275264509</v>
+        <v>20.75096815047068</v>
       </c>
       <c r="D80">
-        <v>60.6739927526451</v>
+        <v>60.78687815047069</v>
       </c>
       <c r="E80">
-        <v>47.61962</v>
+        <v>48.23691</v>
       </c>
       <c r="F80">
-        <v>48.14862000000001</v>
+        <v>48.76591000000001</v>
       </c>
       <c r="G80">
         <v>8.73</v>
@@ -7963,28 +7963,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M80">
-        <v>3.649665396000001</v>
+        <v>3.696455978000001</v>
       </c>
       <c r="N80">
-        <v>4.800334603999998</v>
+        <v>4.753544021999998</v>
       </c>
       <c r="O80">
-        <v>1.200083650999999</v>
+        <v>1.1883860055</v>
       </c>
       <c r="P80">
-        <v>3.600250952999998</v>
+        <v>3.565158016499999</v>
       </c>
       <c r="Q80">
-        <v>3.530250953</v>
+        <v>3.4951580165</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5063668285417288</v>
+        <v>0.5268001394796937</v>
       </c>
       <c r="T80">
-        <v>4.454033235117366</v>
+        <v>4.651638968707312</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.315280740327899</v>
+        <v>2.285973389184508</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8009,22 +8009,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1555395292907357</v>
+        <v>0.155335356302291</v>
       </c>
       <c r="C81">
-        <v>20.75096815047068</v>
+        <v>20.24698438317194</v>
       </c>
       <c r="D81">
-        <v>60.78687815047069</v>
+        <v>60.90018438317195</v>
       </c>
       <c r="E81">
-        <v>48.23691</v>
+        <v>48.85420000000001</v>
       </c>
       <c r="F81">
-        <v>48.76591000000001</v>
+        <v>49.38320000000001</v>
       </c>
       <c r="G81">
         <v>8.73</v>
@@ -8045,28 +8045,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M81">
-        <v>3.696455978000001</v>
+        <v>3.743246560000001</v>
       </c>
       <c r="N81">
-        <v>4.753544021999998</v>
+        <v>4.706753439999998</v>
       </c>
       <c r="O81">
-        <v>1.1883860055</v>
+        <v>1.17668836</v>
       </c>
       <c r="P81">
-        <v>3.565158016499999</v>
+        <v>3.530065079999999</v>
       </c>
       <c r="Q81">
-        <v>3.4951580165</v>
+        <v>3.46006508</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5268001394796937</v>
+        <v>0.5492767815114551</v>
       </c>
       <c r="T81">
-        <v>4.651638968707312</v>
+        <v>4.869005275656252</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.285973389184508</v>
+        <v>2.257398721819702</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8091,22 +8091,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.155335356302291</v>
+        <v>0.1551311833138463</v>
       </c>
       <c r="C82">
-        <v>20.24698438317194</v>
+        <v>19.74342380844167</v>
       </c>
       <c r="D82">
-        <v>60.90018438317195</v>
+        <v>61.01391380844168</v>
       </c>
       <c r="E82">
-        <v>48.85420000000001</v>
+        <v>49.47149</v>
       </c>
       <c r="F82">
-        <v>49.38320000000001</v>
+        <v>50.00049000000001</v>
       </c>
       <c r="G82">
         <v>8.73</v>
@@ -8127,28 +8127,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M82">
-        <v>3.743246560000001</v>
+        <v>3.790037142000001</v>
       </c>
       <c r="N82">
-        <v>4.706753439999998</v>
+        <v>4.659962857999998</v>
       </c>
       <c r="O82">
-        <v>1.17668836</v>
+        <v>1.1649907145</v>
       </c>
       <c r="P82">
-        <v>3.530065079999999</v>
+        <v>3.494972143499999</v>
       </c>
       <c r="Q82">
-        <v>3.46006508</v>
+        <v>3.4249721435</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5492767815114551</v>
+        <v>0.5741193858623493</v>
       </c>
       <c r="T82">
-        <v>4.869005275656252</v>
+        <v>5.109252246494554</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.257398721819702</v>
+        <v>2.229529601797237</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8173,22 +8173,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1551311833138463</v>
+        <v>0.1549270103254017</v>
       </c>
       <c r="C83">
-        <v>19.74342380844167</v>
+        <v>19.24028880161733</v>
       </c>
       <c r="D83">
-        <v>61.01391380844168</v>
+        <v>61.12806880161733</v>
       </c>
       <c r="E83">
-        <v>49.47149</v>
+        <v>50.08878000000001</v>
       </c>
       <c r="F83">
-        <v>50.00049000000001</v>
+        <v>50.61778000000001</v>
       </c>
       <c r="G83">
         <v>8.73</v>
@@ -8209,28 +8209,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M83">
-        <v>3.790037142000001</v>
+        <v>3.836827724000001</v>
       </c>
       <c r="N83">
-        <v>4.659962857999998</v>
+        <v>4.613172275999998</v>
       </c>
       <c r="O83">
-        <v>1.1649907145</v>
+        <v>1.153293069</v>
       </c>
       <c r="P83">
-        <v>3.494972143499999</v>
+        <v>3.459879206999999</v>
       </c>
       <c r="Q83">
-        <v>3.4249721435</v>
+        <v>3.389879207</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5741193858623493</v>
+        <v>0.601722279585565</v>
       </c>
       <c r="T83">
-        <v>5.109252246494554</v>
+        <v>5.376193325203778</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.229529601797237</v>
+        <v>2.202340216409465</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8255,22 +8255,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1549270103254017</v>
+        <v>0.154722837336957</v>
       </c>
       <c r="C84">
-        <v>19.24028880161733</v>
+        <v>18.73758175584635</v>
       </c>
       <c r="D84">
-        <v>61.12806880161733</v>
+        <v>61.24265175584635</v>
       </c>
       <c r="E84">
-        <v>50.08878000000001</v>
+        <v>50.70607</v>
       </c>
       <c r="F84">
-        <v>50.61778000000001</v>
+        <v>51.23507000000001</v>
       </c>
       <c r="G84">
         <v>8.73</v>
@@ -8291,28 +8291,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M84">
-        <v>3.836827724000001</v>
+        <v>3.883618306000001</v>
       </c>
       <c r="N84">
-        <v>4.613172275999998</v>
+        <v>4.566381693999999</v>
       </c>
       <c r="O84">
-        <v>1.153293069</v>
+        <v>1.1415954235</v>
       </c>
       <c r="P84">
-        <v>3.459879206999999</v>
+        <v>3.424786270499999</v>
       </c>
       <c r="Q84">
-        <v>3.389879207</v>
+        <v>3.3547862705</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.601722279585565</v>
+        <v>0.6325725725703357</v>
       </c>
       <c r="T84">
-        <v>5.376193325203778</v>
+        <v>5.674539236702325</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.202340216409465</v>
+        <v>2.175805996934653</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8337,22 +8337,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.154722837336957</v>
+        <v>0.1545186643485124</v>
       </c>
       <c r="C85">
-        <v>18.73758175584635</v>
+        <v>18.23530508225353</v>
       </c>
       <c r="D85">
-        <v>61.24265175584635</v>
+        <v>61.35766508225353</v>
       </c>
       <c r="E85">
-        <v>50.70607</v>
+        <v>51.32336000000001</v>
       </c>
       <c r="F85">
-        <v>51.23507000000001</v>
+        <v>51.85236000000001</v>
       </c>
       <c r="G85">
         <v>8.73</v>
@@ -8373,28 +8373,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M85">
-        <v>3.883618306000001</v>
+        <v>3.930408888000001</v>
       </c>
       <c r="N85">
-        <v>4.566381693999999</v>
+        <v>4.519591111999999</v>
       </c>
       <c r="O85">
-        <v>1.1415954235</v>
+        <v>1.129897778</v>
       </c>
       <c r="P85">
-        <v>3.424786270499999</v>
+        <v>3.389693333999999</v>
       </c>
       <c r="Q85">
-        <v>3.3547862705</v>
+        <v>3.319693334000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6325725725703357</v>
+        <v>0.6672791521782026</v>
       </c>
       <c r="T85">
-        <v>5.674539236702325</v>
+        <v>6.010178387138188</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.175805996934653</v>
+        <v>2.149903544590193</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8419,22 +8419,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1545186643485124</v>
+        <v>0.1543144913600678</v>
       </c>
       <c r="C86">
-        <v>18.2353050822535</v>
+        <v>17.73346121010992</v>
       </c>
       <c r="D86">
-        <v>61.35766508225351</v>
+        <v>61.47311121010993</v>
       </c>
       <c r="E86">
-        <v>51.32336</v>
+        <v>51.94065</v>
       </c>
       <c r="F86">
-        <v>51.85236</v>
+        <v>52.46965</v>
       </c>
       <c r="G86">
         <v>8.73</v>
@@ -8455,28 +8455,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M86">
-        <v>3.930408888000001</v>
+        <v>3.97719947</v>
       </c>
       <c r="N86">
-        <v>4.519591111999999</v>
+        <v>4.472800529999999</v>
       </c>
       <c r="O86">
-        <v>1.129897778</v>
+        <v>1.1182001325</v>
       </c>
       <c r="P86">
-        <v>3.389693333999999</v>
+        <v>3.354600397499999</v>
       </c>
       <c r="Q86">
-        <v>3.319693334000001</v>
+        <v>3.284600397500001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6672791521782022</v>
+        <v>0.7066132757337847</v>
       </c>
       <c r="T86">
-        <v>6.010178387138184</v>
+        <v>6.39056942429883</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.149903544590193</v>
+        <v>2.124610561712661</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8501,22 +8501,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1543144913600678</v>
+        <v>0.1541103183716231</v>
       </c>
       <c r="C87">
-        <v>17.73346121010992</v>
+        <v>17.2320525870042</v>
       </c>
       <c r="D87">
-        <v>61.47311121010993</v>
+        <v>61.58899258700421</v>
       </c>
       <c r="E87">
-        <v>51.94065</v>
+        <v>52.55794</v>
       </c>
       <c r="F87">
-        <v>52.46965</v>
+        <v>53.08694000000001</v>
       </c>
       <c r="G87">
         <v>8.73</v>
@@ -8537,28 +8537,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M87">
-        <v>3.97719947</v>
+        <v>4.023990052000001</v>
       </c>
       <c r="N87">
-        <v>4.472800529999999</v>
+        <v>4.426009947999998</v>
       </c>
       <c r="O87">
-        <v>1.1182001325</v>
+        <v>1.106502487</v>
       </c>
       <c r="P87">
-        <v>3.354600397499999</v>
+        <v>3.319507460999999</v>
       </c>
       <c r="Q87">
-        <v>3.284600397500001</v>
+        <v>3.249507461</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7066132757337847</v>
+        <v>0.7515665597973075</v>
       </c>
       <c r="T87">
-        <v>6.39056942429883</v>
+        <v>6.825302038196709</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.124610561712661</v>
+        <v>2.099905787739258</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8583,22 +8583,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1541103183716231</v>
+        <v>0.1539061453831784</v>
       </c>
       <c r="C88">
-        <v>17.2320525870042</v>
+        <v>16.73108167901525</v>
       </c>
       <c r="D88">
-        <v>61.58899258700421</v>
+        <v>61.70531167901526</v>
       </c>
       <c r="E88">
-        <v>52.55794</v>
+        <v>53.17523</v>
       </c>
       <c r="F88">
-        <v>53.08694000000001</v>
+        <v>53.70423</v>
       </c>
       <c r="G88">
         <v>8.73</v>
@@ -8619,28 +8619,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M88">
-        <v>4.023990052000001</v>
+        <v>4.070780634</v>
       </c>
       <c r="N88">
-        <v>4.426009947999998</v>
+        <v>4.379219365999999</v>
       </c>
       <c r="O88">
-        <v>1.106502487</v>
+        <v>1.0948048415</v>
       </c>
       <c r="P88">
-        <v>3.319507460999999</v>
+        <v>3.284414524499999</v>
       </c>
       <c r="Q88">
-        <v>3.249507461</v>
+        <v>3.214414524500001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7515665597973075</v>
+        <v>0.8034357337167567</v>
       </c>
       <c r="T88">
-        <v>6.825302038196709</v>
+        <v>7.326916592694261</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.099905787739258</v>
+        <v>2.075768939604324</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8665,22 +8665,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1539061453831784</v>
+        <v>0.1537019723947337</v>
       </c>
       <c r="C89">
-        <v>16.73108167901525</v>
+        <v>16.23055097088736</v>
       </c>
       <c r="D89">
-        <v>61.70531167901526</v>
+        <v>61.82207097088737</v>
       </c>
       <c r="E89">
-        <v>53.17523</v>
+        <v>53.79252</v>
       </c>
       <c r="F89">
-        <v>53.70423</v>
+        <v>54.32152000000001</v>
       </c>
       <c r="G89">
         <v>8.73</v>
@@ -8701,28 +8701,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M89">
-        <v>4.070780634</v>
+        <v>4.117571216000001</v>
       </c>
       <c r="N89">
-        <v>4.379219365999999</v>
+        <v>4.332428783999998</v>
       </c>
       <c r="O89">
-        <v>1.0948048415</v>
+        <v>1.083107196</v>
       </c>
       <c r="P89">
-        <v>3.284414524499999</v>
+        <v>3.249321587999999</v>
       </c>
       <c r="Q89">
-        <v>3.214414524500001</v>
+        <v>3.179321588000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8034357337167567</v>
+        <v>0.8639497699561144</v>
       </c>
       <c r="T89">
-        <v>7.326916592694261</v>
+        <v>7.912133572941408</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.075768939604324</v>
+        <v>2.052180656199729</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8747,22 +8747,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1537019723947337</v>
+        <v>0.153497799406289</v>
       </c>
       <c r="C90">
-        <v>16.23055097088736</v>
+        <v>15.73046296620713</v>
       </c>
       <c r="D90">
-        <v>61.82207097088737</v>
+        <v>61.93927296620713</v>
       </c>
       <c r="E90">
-        <v>53.79252</v>
+        <v>54.40981</v>
       </c>
       <c r="F90">
-        <v>54.32152000000001</v>
+        <v>54.93881</v>
       </c>
       <c r="G90">
         <v>8.73</v>
@@ -8783,28 +8783,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M90">
-        <v>4.117571216000001</v>
+        <v>4.164361798000001</v>
       </c>
       <c r="N90">
-        <v>4.332428783999998</v>
+        <v>4.285638201999999</v>
       </c>
       <c r="O90">
-        <v>1.083107196</v>
+        <v>1.0714095505</v>
       </c>
       <c r="P90">
-        <v>3.249321587999999</v>
+        <v>3.214228651499999</v>
       </c>
       <c r="Q90">
-        <v>3.179321588000001</v>
+        <v>3.144228651500001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8639497699561144</v>
+        <v>0.9354663582389915</v>
       </c>
       <c r="T90">
-        <v>7.912133572941408</v>
+        <v>8.603753640506216</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.052180656199729</v>
+        <v>2.029122446579508</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8829,22 +8829,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.153497799406289</v>
+        <v>0.1532936264178444</v>
       </c>
       <c r="C91">
-        <v>15.73046296620713</v>
+        <v>15.23082018758227</v>
       </c>
       <c r="D91">
-        <v>61.93927296620713</v>
+        <v>62.05692018758228</v>
       </c>
       <c r="E91">
-        <v>54.40981</v>
+        <v>55.0271</v>
       </c>
       <c r="F91">
-        <v>54.93881</v>
+        <v>55.55610000000001</v>
       </c>
       <c r="G91">
         <v>8.73</v>
@@ -8865,28 +8865,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M91">
-        <v>4.164361798000001</v>
+        <v>4.211152380000001</v>
       </c>
       <c r="N91">
-        <v>4.285638201999999</v>
+        <v>4.238847619999999</v>
       </c>
       <c r="O91">
-        <v>1.0714095505</v>
+        <v>1.059711905</v>
       </c>
       <c r="P91">
-        <v>3.214228651499999</v>
+        <v>3.179135714999999</v>
       </c>
       <c r="Q91">
-        <v>3.144228651500001</v>
+        <v>3.109135715000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9354663582389915</v>
+        <v>1.021286264178445</v>
       </c>
       <c r="T91">
-        <v>8.603753640506216</v>
+        <v>9.433697721583989</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.029122446579508</v>
+        <v>2.006576641617513</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8911,22 +8911,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1532936264178444</v>
+        <v>0.1627809534293998</v>
       </c>
       <c r="C92">
-        <v>15.23082018758227</v>
+        <v>9.580622881822386</v>
       </c>
       <c r="D92">
-        <v>62.05692018758228</v>
+        <v>57.02401288182239</v>
       </c>
       <c r="E92">
-        <v>55.0271</v>
+        <v>55.64439</v>
       </c>
       <c r="F92">
-        <v>55.55610000000001</v>
+        <v>56.17339</v>
       </c>
       <c r="G92">
         <v>8.73</v>
@@ -8947,45 +8947,45 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M92">
-        <v>4.211152380000001</v>
+        <v>5.0556051</v>
       </c>
       <c r="N92">
-        <v>4.238847619999999</v>
+        <v>3.394394899999999</v>
       </c>
       <c r="O92">
-        <v>1.059711905</v>
+        <v>0.8485987249999998</v>
       </c>
       <c r="P92">
-        <v>3.179135714999999</v>
+        <v>2.545796175</v>
       </c>
       <c r="Q92">
-        <v>3.109135715000001</v>
+        <v>2.475796175000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.021286264178445</v>
+        <v>1.126177260326664</v>
       </c>
       <c r="T92">
-        <v>9.433697721583989</v>
+        <v>10.44807382067904</v>
       </c>
       <c r="U92">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.006576641617513</v>
+        <v>1.671412191589094</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8993,22 +8993,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1627809534293998</v>
+        <v>0.1626832804409551</v>
       </c>
       <c r="C93">
-        <v>9.580622881822386</v>
+        <v>9.010984742124919</v>
       </c>
       <c r="D93">
-        <v>57.02401288182239</v>
+        <v>57.07166474212492</v>
       </c>
       <c r="E93">
-        <v>55.64439</v>
+        <v>56.26168000000001</v>
       </c>
       <c r="F93">
-        <v>56.17339</v>
+        <v>56.79068000000001</v>
       </c>
       <c r="G93">
         <v>8.73</v>
@@ -9029,28 +9029,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M93">
-        <v>5.0556051</v>
+        <v>5.111161200000001</v>
       </c>
       <c r="N93">
-        <v>3.394394899999999</v>
+        <v>3.338838799999999</v>
       </c>
       <c r="O93">
-        <v>0.8485987249999998</v>
+        <v>0.8347096999999997</v>
       </c>
       <c r="P93">
-        <v>2.545796175</v>
+        <v>2.504129099999999</v>
       </c>
       <c r="Q93">
-        <v>2.475796175000001</v>
+        <v>2.434129100000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.126177260326664</v>
+        <v>1.25729100551194</v>
       </c>
       <c r="T93">
-        <v>10.44807382067904</v>
+        <v>11.71604394454786</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.671412191589094</v>
+        <v>1.653244667767473</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9075,22 +9075,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1626832804409551</v>
+        <v>0.1625856074525104</v>
       </c>
       <c r="C94">
-        <v>9.010984742124919</v>
+        <v>8.441426309160207</v>
       </c>
       <c r="D94">
-        <v>57.07166474212492</v>
+        <v>57.11939630916021</v>
       </c>
       <c r="E94">
-        <v>56.26168000000001</v>
+        <v>56.87897</v>
       </c>
       <c r="F94">
-        <v>56.79068000000001</v>
+        <v>57.40797000000001</v>
       </c>
       <c r="G94">
         <v>8.73</v>
@@ -9111,28 +9111,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M94">
-        <v>5.111161200000001</v>
+        <v>5.1667173</v>
       </c>
       <c r="N94">
-        <v>3.338838799999999</v>
+        <v>3.283282699999999</v>
       </c>
       <c r="O94">
-        <v>0.8347096999999997</v>
+        <v>0.8208206749999998</v>
       </c>
       <c r="P94">
-        <v>2.504129099999999</v>
+        <v>2.462462024999999</v>
       </c>
       <c r="Q94">
-        <v>2.434129100000001</v>
+        <v>2.392462025000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.25729100551194</v>
+        <v>1.42586582075015</v>
       </c>
       <c r="T94">
-        <v>11.71604394454786</v>
+        <v>13.34629124666491</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.653244667767473</v>
+        <v>1.635467843382877</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9157,22 +9157,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1625856074525104</v>
+        <v>0.1624879344640658</v>
       </c>
       <c r="C95">
-        <v>8.441426309160207</v>
+        <v>7.871947783082454</v>
       </c>
       <c r="D95">
-        <v>57.11939630916021</v>
+        <v>57.16720778308247</v>
       </c>
       <c r="E95">
-        <v>56.87897</v>
+        <v>57.49626000000001</v>
       </c>
       <c r="F95">
-        <v>57.40797000000001</v>
+        <v>58.02526000000001</v>
       </c>
       <c r="G95">
         <v>8.73</v>
@@ -9193,28 +9193,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M95">
-        <v>5.1667173</v>
+        <v>5.222273400000001</v>
       </c>
       <c r="N95">
-        <v>3.283282699999999</v>
+        <v>3.227726599999999</v>
       </c>
       <c r="O95">
-        <v>0.8208206749999998</v>
+        <v>0.8069316499999997</v>
       </c>
       <c r="P95">
-        <v>2.462462024999999</v>
+        <v>2.420794949999999</v>
       </c>
       <c r="Q95">
-        <v>2.392462025000001</v>
+        <v>2.35079495</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.42586582075015</v>
+        <v>1.650632241067765</v>
       </c>
       <c r="T95">
-        <v>13.34629124666491</v>
+        <v>15.51995431615431</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.635467843382877</v>
+        <v>1.618069249304335</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9239,22 +9239,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1624879344640658</v>
+        <v>0.1623902614756211</v>
       </c>
       <c r="C96">
-        <v>7.871947783082454</v>
+        <v>7.302549364716647</v>
       </c>
       <c r="D96">
-        <v>57.16720778308247</v>
+        <v>57.21509936471665</v>
       </c>
       <c r="E96">
-        <v>57.49626000000001</v>
+        <v>58.11355</v>
       </c>
       <c r="F96">
-        <v>58.02526000000001</v>
+        <v>58.64255000000001</v>
       </c>
       <c r="G96">
         <v>8.73</v>
@@ -9275,28 +9275,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M96">
-        <v>5.222273400000001</v>
+        <v>5.2778295</v>
       </c>
       <c r="N96">
-        <v>3.227726599999999</v>
+        <v>3.172170499999999</v>
       </c>
       <c r="O96">
-        <v>0.8069316499999997</v>
+        <v>0.7930426249999998</v>
       </c>
       <c r="P96">
-        <v>2.420794949999999</v>
+        <v>2.379127874999999</v>
       </c>
       <c r="Q96">
-        <v>2.35079495</v>
+        <v>2.309127875000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.650632241067765</v>
+        <v>1.965305229512425</v>
       </c>
       <c r="T96">
-        <v>15.51995431615431</v>
+        <v>18.56308261343948</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.618069249304335</v>
+        <v>1.601036941416921</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9321,22 +9321,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1623902614756211</v>
+        <v>0.1622925884871765</v>
       </c>
       <c r="C97">
-        <v>7.302549364716647</v>
+        <v>6.733231255561222</v>
       </c>
       <c r="D97">
-        <v>57.21509936471665</v>
+        <v>57.26307125556123</v>
       </c>
       <c r="E97">
-        <v>58.11355</v>
+        <v>58.73084000000001</v>
       </c>
       <c r="F97">
-        <v>58.64255000000001</v>
+        <v>59.25984000000001</v>
       </c>
       <c r="G97">
         <v>8.73</v>
@@ -9357,28 +9357,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M97">
-        <v>5.2778295</v>
+        <v>5.333385600000001</v>
       </c>
       <c r="N97">
-        <v>3.172170499999999</v>
+        <v>3.116614399999999</v>
       </c>
       <c r="O97">
-        <v>0.7930426249999998</v>
+        <v>0.7791535999999997</v>
       </c>
       <c r="P97">
-        <v>2.379127874999999</v>
+        <v>2.337460799999999</v>
       </c>
       <c r="Q97">
-        <v>2.309127875000001</v>
+        <v>2.2674608</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.965305229512425</v>
+        <v>2.437314712179416</v>
       </c>
       <c r="T97">
-        <v>18.56308261343948</v>
+        <v>23.12777505936724</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.601036941416921</v>
+        <v>1.584359473277162</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9403,22 +9403,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1622925884871765</v>
+        <v>0.1621949154987318</v>
       </c>
       <c r="C98">
-        <v>6.733231255561229</v>
+        <v>6.163993657791032</v>
       </c>
       <c r="D98">
-        <v>57.26307125556123</v>
+        <v>57.31112365779104</v>
       </c>
       <c r="E98">
-        <v>58.73084</v>
+        <v>59.34813</v>
       </c>
       <c r="F98">
-        <v>59.25984</v>
+        <v>59.87713</v>
       </c>
       <c r="G98">
         <v>8.73</v>
@@ -9439,28 +9439,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M98">
-        <v>5.3333856</v>
+        <v>5.3889417</v>
       </c>
       <c r="N98">
-        <v>3.1166144</v>
+        <v>3.061058299999999</v>
       </c>
       <c r="O98">
-        <v>0.7791535999999999</v>
+        <v>0.7652645749999998</v>
       </c>
       <c r="P98">
-        <v>2.3374608</v>
+        <v>2.295793724999999</v>
       </c>
       <c r="Q98">
-        <v>2.267460800000001</v>
+        <v>2.225793725000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.43731471217941</v>
+        <v>3.223997183291057</v>
       </c>
       <c r="T98">
-        <v>23.12777505936718</v>
+        <v>30.73559580258006</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.584359473277162</v>
+        <v>1.568025870459871</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9485,22 +9485,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1621949154987318</v>
+        <v>0.1620972425102872</v>
       </c>
       <c r="C99">
-        <v>6.163993657791032</v>
+        <v>5.594836774260088</v>
       </c>
       <c r="D99">
-        <v>57.31112365779104</v>
+        <v>57.35925677426009</v>
       </c>
       <c r="E99">
-        <v>59.34813</v>
+        <v>59.96542</v>
       </c>
       <c r="F99">
-        <v>59.87713</v>
+        <v>60.49442000000001</v>
       </c>
       <c r="G99">
         <v>8.73</v>
@@ -9521,28 +9521,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M99">
-        <v>5.3889417</v>
+        <v>5.444497800000001</v>
       </c>
       <c r="N99">
-        <v>3.061058299999999</v>
+        <v>3.005502199999999</v>
       </c>
       <c r="O99">
-        <v>0.7652645749999998</v>
+        <v>0.7513755499999997</v>
       </c>
       <c r="P99">
-        <v>2.295793724999999</v>
+        <v>2.254126649999999</v>
       </c>
       <c r="Q99">
-        <v>2.225793725000001</v>
+        <v>2.184126650000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.223997183291057</v>
+        <v>4.797362125514354</v>
       </c>
       <c r="T99">
-        <v>30.73559580258006</v>
+        <v>45.95123728900584</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.568025870459871</v>
+        <v>1.552025606475587</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9567,22 +9567,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1620972425102872</v>
+        <v>0.1619995695218425</v>
       </c>
       <c r="C100">
-        <v>5.594836774260088</v>
+        <v>5.025760808504444</v>
       </c>
       <c r="D100">
-        <v>57.35925677426009</v>
+        <v>57.40747080850445</v>
       </c>
       <c r="E100">
-        <v>59.96542</v>
+        <v>60.58271</v>
       </c>
       <c r="F100">
-        <v>60.49442000000001</v>
+        <v>61.11171</v>
       </c>
       <c r="G100">
         <v>8.73</v>
@@ -9603,28 +9603,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="M100">
-        <v>5.444497800000001</v>
+        <v>5.5000539</v>
       </c>
       <c r="N100">
-        <v>3.005502199999999</v>
+        <v>2.949946099999999</v>
       </c>
       <c r="O100">
-        <v>0.7513755499999997</v>
+        <v>0.7374865249999998</v>
       </c>
       <c r="P100">
-        <v>2.254126649999999</v>
+        <v>2.212459575</v>
       </c>
       <c r="Q100">
-        <v>2.184126650000001</v>
+        <v>2.142459575000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.797362125514354</v>
+        <v>9.517456952184242</v>
       </c>
       <c r="T100">
-        <v>45.95123728900584</v>
+        <v>91.59816174828316</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9641,91 +9641,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.552025606475587</v>
+        <v>1.536348580147551</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1619995695218425</v>
-      </c>
-      <c r="C101">
-        <v>5.025760808504444</v>
-      </c>
-      <c r="D101">
-        <v>57.40747080850445</v>
-      </c>
-      <c r="E101">
-        <v>60.58271</v>
-      </c>
-      <c r="F101">
-        <v>61.11171</v>
-      </c>
-      <c r="G101">
-        <v>8.73</v>
-      </c>
-      <c r="H101">
-        <v>61.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="K101">
-        <v>-0.06999999999999851</v>
-      </c>
-      <c r="L101">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="M101">
-        <v>5.5000539</v>
-      </c>
-      <c r="N101">
-        <v>2.949946099999999</v>
-      </c>
-      <c r="O101">
-        <v>0.7374865249999998</v>
-      </c>
-      <c r="P101">
-        <v>2.212459575</v>
-      </c>
-      <c r="Q101">
-        <v>2.142459575000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.517456952184242</v>
-      </c>
-      <c r="T101">
-        <v>91.59816174828316</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.0675</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.536348580147551</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
